--- a/artfynd/A 64501-2023 artfynd.xlsx
+++ b/artfynd/A 64501-2023 artfynd.xlsx
@@ -776,32 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126839924</v>
+        <v>126836222</v>
       </c>
       <c r="B3" t="n">
-        <v>75075</v>
+        <v>91284</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>680859</v>
+        <v>680864</v>
       </c>
       <c r="R3" t="n">
-        <v>7087090</v>
+        <v>7087088</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,12 +861,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -877,32 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126836222</v>
+        <v>126839924</v>
       </c>
       <c r="B4" t="n">
-        <v>91210</v>
+        <v>75135</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>6440</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>680864</v>
+        <v>680859</v>
       </c>
       <c r="R4" t="n">
-        <v>7087088</v>
+        <v>7087090</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -962,12 +962,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -978,10 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126836455</v>
+        <v>126836264</v>
       </c>
       <c r="B5" t="n">
-        <v>78980</v>
+        <v>57657</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -989,34 +989,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>680796</v>
+        <v>680811</v>
       </c>
       <c r="R5" t="n">
-        <v>7087097</v>
+        <v>7087049</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1049,6 +1054,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1079,45 +1089,49 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126836243</v>
+        <v>126836229</v>
       </c>
       <c r="B6" t="n">
-        <v>98382</v>
+        <v>57657</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>680867</v>
+        <v>680850</v>
       </c>
       <c r="R6" t="n">
-        <v>7087092</v>
+        <v>7087177</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1180,10 +1194,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126836264</v>
+        <v>126839930</v>
       </c>
       <c r="B7" t="n">
-        <v>57657</v>
+        <v>75135</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,39 +1205,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>680811</v>
+        <v>680800</v>
       </c>
       <c r="R7" t="n">
-        <v>7087049</v>
+        <v>7087070</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1258,11 +1267,6 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>äldre ringhack (gran)</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1275,12 +1279,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1291,10 +1295,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126836229</v>
+        <v>126836455</v>
       </c>
       <c r="B8" t="n">
-        <v>57657</v>
+        <v>79011</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1302,38 +1306,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>680850</v>
+        <v>680796</v>
       </c>
       <c r="R8" t="n">
-        <v>7087177</v>
+        <v>7087097</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1396,32 +1396,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126839930</v>
+        <v>126836243</v>
       </c>
       <c r="B9" t="n">
-        <v>75075</v>
+        <v>98457</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>221952</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>680800</v>
+        <v>680867</v>
       </c>
       <c r="R9" t="n">
-        <v>7087070</v>
+        <v>7087092</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1481,12 +1481,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1497,50 +1497,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126836499</v>
+        <v>126836248</v>
       </c>
       <c r="B10" t="n">
-        <v>57657</v>
+        <v>80018</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>680839</v>
+        <v>680890</v>
       </c>
       <c r="R10" t="n">
-        <v>7087048</v>
+        <v>7086899</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1603,45 +1598,50 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126836248</v>
+        <v>126839943</v>
       </c>
       <c r="B11" t="n">
-        <v>79987</v>
+        <v>57657</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>680890</v>
+        <v>680794</v>
       </c>
       <c r="R11" t="n">
-        <v>7086899</v>
+        <v>7087085</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1688,12 +1688,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1704,7 +1704,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126836500</v>
+        <v>126836499</v>
       </c>
       <c r="B12" t="n">
         <v>57657</v>
@@ -1744,10 +1744,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>680809</v>
+        <v>680839</v>
       </c>
       <c r="R12" t="n">
-        <v>7087115</v>
+        <v>7087048</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1810,7 +1810,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126839943</v>
+        <v>126836500</v>
       </c>
       <c r="B13" t="n">
         <v>57657</v>
@@ -1841,7 +1841,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1850,10 +1850,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>680794</v>
+        <v>680809</v>
       </c>
       <c r="R13" t="n">
-        <v>7087085</v>
+        <v>7087115</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1900,12 +1900,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1919,7 +1919,7 @@
         <v>126839925</v>
       </c>
       <c r="B14" t="n">
-        <v>75061</v>
+        <v>75120</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2017,10 +2017,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126836451</v>
+        <v>126836260</v>
       </c>
       <c r="B15" t="n">
-        <v>78980</v>
+        <v>57657</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2028,34 +2028,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>680864</v>
+        <v>680809</v>
       </c>
       <c r="R15" t="n">
-        <v>7087091</v>
+        <v>7087061</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2088,6 +2093,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran) intill djupa körspår efter illegal avverkning genomförd av SCA</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2118,10 +2128,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126836465</v>
+        <v>126836258</v>
       </c>
       <c r="B16" t="n">
-        <v>78980</v>
+        <v>57657</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2129,34 +2139,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>680782</v>
+        <v>680805</v>
       </c>
       <c r="R16" t="n">
-        <v>7087268</v>
+        <v>7087122</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2189,6 +2204,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran) intill djupa körspår efter illegal avverkning genomförd av SCA</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2219,10 +2239,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126836260</v>
+        <v>126836451</v>
       </c>
       <c r="B17" t="n">
-        <v>57657</v>
+        <v>79011</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2230,39 +2250,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>680809</v>
+        <v>680864</v>
       </c>
       <c r="R17" t="n">
-        <v>7087061</v>
+        <v>7087091</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2295,11 +2310,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran) intill djupa körspår efter illegal avverkning genomförd av SCA</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2330,10 +2340,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126836258</v>
+        <v>126836465</v>
       </c>
       <c r="B18" t="n">
-        <v>57657</v>
+        <v>79011</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2341,39 +2351,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>680805</v>
+        <v>680782</v>
       </c>
       <c r="R18" t="n">
-        <v>7087122</v>
+        <v>7087268</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2406,11 +2411,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran) intill djupa körspår efter illegal avverkning genomförd av SCA</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2441,10 +2441,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126840006</v>
+        <v>126836282</v>
       </c>
       <c r="B19" t="n">
-        <v>8436</v>
+        <v>80142</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2452,21 +2452,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106554</v>
+        <v>6461</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2476,10 +2476,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>680902</v>
+        <v>680867</v>
       </c>
       <c r="R19" t="n">
-        <v>7087115</v>
+        <v>7087092</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2526,12 +2526,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2542,32 +2542,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126836282</v>
+        <v>126836452</v>
       </c>
       <c r="B20" t="n">
-        <v>80111</v>
+        <v>79011</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2577,10 +2577,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>680867</v>
+        <v>680856</v>
       </c>
       <c r="R20" t="n">
-        <v>7087092</v>
+        <v>7087078</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2643,32 +2643,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126836452</v>
+        <v>126840006</v>
       </c>
       <c r="B21" t="n">
-        <v>78980</v>
+        <v>8436</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>106554</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2678,10 +2678,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>680856</v>
+        <v>680902</v>
       </c>
       <c r="R21" t="n">
-        <v>7087078</v>
+        <v>7087115</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2728,12 +2728,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2747,7 +2747,7 @@
         <v>126839980</v>
       </c>
       <c r="B22" t="n">
-        <v>75061</v>
+        <v>75120</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2845,45 +2845,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126836454</v>
+        <v>126838808</v>
       </c>
       <c r="B23" t="n">
-        <v>78980</v>
+        <v>58027</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Röjdtjärnviden, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>680813</v>
+        <v>680797</v>
       </c>
       <c r="R23" t="n">
-        <v>7087014</v>
+        <v>7087093</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2930,12 +2930,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -2946,45 +2946,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126838808</v>
+        <v>126836454</v>
       </c>
       <c r="B24" t="n">
-        <v>58027</v>
+        <v>79011</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Röjdtjärnviden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>680797</v>
+        <v>680813</v>
       </c>
       <c r="R24" t="n">
-        <v>7087093</v>
+        <v>7087014</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3031,12 +3031,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3050,7 +3050,7 @@
         <v>126836283</v>
       </c>
       <c r="B25" t="n">
-        <v>80111</v>
+        <v>80142</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         <v>126840775</v>
       </c>
       <c r="B26" t="n">
-        <v>78647</v>
+        <v>78678</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3263,10 +3263,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126836223</v>
+        <v>126826864</v>
       </c>
       <c r="B27" t="n">
-        <v>91210</v>
+        <v>80149</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3274,34 +3274,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>6463</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Slagörkullen, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>680802</v>
+        <v>680792</v>
       </c>
       <c r="R27" t="n">
-        <v>7087182</v>
+        <v>7087098</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3331,9 +3331,19 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3348,12 +3358,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3367,7 +3377,7 @@
         <v>126836456</v>
       </c>
       <c r="B28" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3465,10 +3475,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126826864</v>
+        <v>126836223</v>
       </c>
       <c r="B29" t="n">
-        <v>80118</v>
+        <v>91284</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3476,34 +3486,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6463</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Slagörkullen, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>680792</v>
+        <v>680802</v>
       </c>
       <c r="R29" t="n">
-        <v>7087098</v>
+        <v>7087182</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3533,19 +3543,9 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>11:15</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>11:15</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3560,12 +3560,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3576,10 +3576,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126836448</v>
+        <v>126839926</v>
       </c>
       <c r="B30" t="n">
-        <v>78980</v>
+        <v>75135</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3587,21 +3587,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3611,10 +3611,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>680910</v>
+        <v>680847</v>
       </c>
       <c r="R30" t="n">
-        <v>7087135</v>
+        <v>7087085</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3661,12 +3661,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3677,10 +3677,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126839926</v>
+        <v>126836448</v>
       </c>
       <c r="B31" t="n">
-        <v>75075</v>
+        <v>79011</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3688,21 +3688,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3712,10 +3712,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>680847</v>
+        <v>680910</v>
       </c>
       <c r="R31" t="n">
-        <v>7087085</v>
+        <v>7087135</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3762,12 +3762,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3778,10 +3778,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126836277</v>
+        <v>126836239</v>
       </c>
       <c r="B32" t="n">
-        <v>97239</v>
+        <v>80143</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3789,21 +3789,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221945</v>
+        <v>6462</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3813,10 +3813,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>680850</v>
+        <v>680791</v>
       </c>
       <c r="R32" t="n">
-        <v>7087177</v>
+        <v>7087100</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3879,32 +3879,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126836457</v>
+        <v>126836277</v>
       </c>
       <c r="B33" t="n">
-        <v>78980</v>
+        <v>97314</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3914,10 +3914,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>680830</v>
+        <v>680850</v>
       </c>
       <c r="R33" t="n">
-        <v>7087203</v>
+        <v>7087177</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3980,32 +3980,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126836239</v>
+        <v>126836457</v>
       </c>
       <c r="B34" t="n">
-        <v>80112</v>
+        <v>79011</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4015,10 +4015,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>680791</v>
+        <v>680830</v>
       </c>
       <c r="R34" t="n">
-        <v>7087100</v>
+        <v>7087203</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4186,7 +4186,7 @@
         <v>126836281</v>
       </c>
       <c r="B36" t="n">
-        <v>80111</v>
+        <v>80142</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4287,7 +4287,7 @@
         <v>126839965</v>
       </c>
       <c r="B37" t="n">
-        <v>78739</v>
+        <v>78770</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4388,7 +4388,7 @@
         <v>126836358</v>
       </c>
       <c r="B38" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4486,45 +4486,50 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126836247</v>
+        <v>126836263</v>
       </c>
       <c r="B39" t="n">
-        <v>79987</v>
+        <v>57657</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>680772</v>
+        <v>680847</v>
       </c>
       <c r="R39" t="n">
-        <v>7087294</v>
+        <v>7087070</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4561,7 +4566,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>På asplåga</t>
+          <t>äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4592,50 +4597,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126836263</v>
+        <v>126836247</v>
       </c>
       <c r="B40" t="n">
-        <v>57657</v>
+        <v>80018</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>680847</v>
+        <v>680772</v>
       </c>
       <c r="R40" t="n">
-        <v>7087070</v>
+        <v>7087294</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>äldre ringhack (gran)</t>
+          <t>På asplåga</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4703,10 +4703,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126836450</v>
+        <v>126836359</v>
       </c>
       <c r="B41" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4738,10 +4738,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>680892</v>
+        <v>680826</v>
       </c>
       <c r="R41" t="n">
-        <v>7087111</v>
+        <v>7086953</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4804,10 +4804,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126836359</v>
+        <v>126836450</v>
       </c>
       <c r="B42" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4839,10 +4839,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>680826</v>
+        <v>680892</v>
       </c>
       <c r="R42" t="n">
-        <v>7086953</v>
+        <v>7087111</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4905,10 +4905,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126839966</v>
+        <v>126836265</v>
       </c>
       <c r="B43" t="n">
-        <v>79598</v>
+        <v>57657</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4916,34 +4916,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>680908</v>
+        <v>680876</v>
       </c>
       <c r="R43" t="n">
-        <v>7087111</v>
+        <v>7086899</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4978,6 +4983,11 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>färska ringhack (gran)</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -4990,12 +5000,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5006,10 +5016,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126836266</v>
+        <v>126839966</v>
       </c>
       <c r="B44" t="n">
-        <v>57657</v>
+        <v>79629</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5017,39 +5027,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>680870</v>
+        <v>680908</v>
       </c>
       <c r="R44" t="n">
-        <v>7086922</v>
+        <v>7087111</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5084,11 +5089,6 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Färska ringhack på nyligen tillskapad högstubbe i samband med av SCA genomförd illegal avverkning</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5101,12 +5101,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5117,7 +5117,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126836265</v>
+        <v>126836266</v>
       </c>
       <c r="B45" t="n">
         <v>57657</v>
@@ -5157,10 +5157,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>680876</v>
+        <v>680870</v>
       </c>
       <c r="R45" t="n">
-        <v>7086899</v>
+        <v>7086922</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5197,7 +5197,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>färska ringhack (gran)</t>
+          <t>Färska ringhack på nyligen tillskapad högstubbe i samband med av SCA genomförd illegal avverkning</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5231,7 +5231,7 @@
         <v>126836540</v>
       </c>
       <c r="B46" t="n">
-        <v>78647</v>
+        <v>78678</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5329,10 +5329,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126836453</v>
+        <v>126836212</v>
       </c>
       <c r="B47" t="n">
-        <v>78980</v>
+        <v>75135</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5340,21 +5340,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5364,10 +5364,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>680855</v>
+        <v>680844</v>
       </c>
       <c r="R47" t="n">
-        <v>7087023</v>
+        <v>7087067</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5430,10 +5430,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126836267</v>
+        <v>126836453</v>
       </c>
       <c r="B48" t="n">
-        <v>57657</v>
+        <v>79011</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5441,39 +5441,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>680851</v>
+        <v>680855</v>
       </c>
       <c r="R48" t="n">
-        <v>7087171</v>
+        <v>7087023</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5506,11 +5501,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5541,10 +5531,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126836212</v>
+        <v>126836267</v>
       </c>
       <c r="B49" t="n">
-        <v>75075</v>
+        <v>57657</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5552,34 +5542,39 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>680844</v>
+        <v>680851</v>
       </c>
       <c r="R49" t="n">
-        <v>7087067</v>
+        <v>7087171</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5612,6 +5607,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5642,10 +5642,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126839954</v>
+        <v>126837045</v>
       </c>
       <c r="B50" t="n">
-        <v>57817</v>
+        <v>91319</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5653,34 +5653,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>680871</v>
+        <v>680812</v>
       </c>
       <c r="R50" t="n">
-        <v>7087130</v>
+        <v>7086987</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5727,12 +5727,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -5743,10 +5743,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126837045</v>
+        <v>126839954</v>
       </c>
       <c r="B51" t="n">
-        <v>91245</v>
+        <v>57817</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5754,34 +5754,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>680812</v>
+        <v>680871</v>
       </c>
       <c r="R51" t="n">
-        <v>7086987</v>
+        <v>7087130</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5828,12 +5828,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -5847,7 +5847,7 @@
         <v>126836213</v>
       </c>
       <c r="B52" t="n">
-        <v>75075</v>
+        <v>75135</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5948,7 +5948,7 @@
         <v>126836276</v>
       </c>
       <c r="B53" t="n">
-        <v>97239</v>
+        <v>97314</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6049,7 +6049,7 @@
         <v>126838799</v>
       </c>
       <c r="B54" t="n">
-        <v>98382</v>
+        <v>98457</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 64501-2023 artfynd.xlsx
+++ b/artfynd/A 64501-2023 artfynd.xlsx
@@ -779,7 +779,7 @@
         <v>126836222</v>
       </c>
       <c r="B3" t="n">
-        <v>91284</v>
+        <v>91290</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>126839924</v>
       </c>
       <c r="B4" t="n">
-        <v>75135</v>
+        <v>75138</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1194,32 +1194,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126839930</v>
+        <v>126836243</v>
       </c>
       <c r="B7" t="n">
-        <v>75135</v>
+        <v>98463</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6440</v>
+        <v>221952</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1229,10 +1229,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>680800</v>
+        <v>680867</v>
       </c>
       <c r="R7" t="n">
-        <v>7087070</v>
+        <v>7087092</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1279,12 +1279,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1295,10 +1295,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126836455</v>
+        <v>126839930</v>
       </c>
       <c r="B8" t="n">
-        <v>79011</v>
+        <v>75138</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1306,21 +1306,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1330,10 +1330,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>680796</v>
+        <v>680800</v>
       </c>
       <c r="R8" t="n">
-        <v>7087097</v>
+        <v>7087070</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1380,12 +1380,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1396,32 +1396,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126836243</v>
+        <v>126836455</v>
       </c>
       <c r="B9" t="n">
-        <v>98457</v>
+        <v>79014</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>680867</v>
+        <v>680796</v>
       </c>
       <c r="R9" t="n">
-        <v>7087092</v>
+        <v>7087097</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1497,45 +1497,50 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126836248</v>
+        <v>126839943</v>
       </c>
       <c r="B10" t="n">
-        <v>80018</v>
+        <v>57657</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>680890</v>
+        <v>680794</v>
       </c>
       <c r="R10" t="n">
-        <v>7086899</v>
+        <v>7087085</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1582,12 +1587,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1598,7 +1603,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126839943</v>
+        <v>126836499</v>
       </c>
       <c r="B11" t="n">
         <v>57657</v>
@@ -1629,7 +1634,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1638,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>680794</v>
+        <v>680839</v>
       </c>
       <c r="R11" t="n">
-        <v>7087085</v>
+        <v>7087048</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1688,12 +1693,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1704,7 +1709,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126836499</v>
+        <v>126836500</v>
       </c>
       <c r="B12" t="n">
         <v>57657</v>
@@ -1744,10 +1749,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>680839</v>
+        <v>680809</v>
       </c>
       <c r="R12" t="n">
-        <v>7087048</v>
+        <v>7087115</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1810,50 +1815,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126836500</v>
+        <v>126836248</v>
       </c>
       <c r="B13" t="n">
-        <v>57657</v>
+        <v>80021</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>680809</v>
+        <v>680890</v>
       </c>
       <c r="R13" t="n">
-        <v>7087115</v>
+        <v>7086899</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1919,7 +1919,7 @@
         <v>126839925</v>
       </c>
       <c r="B14" t="n">
-        <v>75120</v>
+        <v>75123</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2017,10 +2017,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126836260</v>
+        <v>126836451</v>
       </c>
       <c r="B15" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2028,39 +2028,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>680809</v>
+        <v>680864</v>
       </c>
       <c r="R15" t="n">
-        <v>7087061</v>
+        <v>7087091</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2093,11 +2088,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran) intill djupa körspår efter illegal avverkning genomförd av SCA</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2128,10 +2118,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126836258</v>
+        <v>126836465</v>
       </c>
       <c r="B16" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2139,39 +2129,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>680805</v>
+        <v>680782</v>
       </c>
       <c r="R16" t="n">
-        <v>7087122</v>
+        <v>7087268</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2204,11 +2189,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran) intill djupa körspår efter illegal avverkning genomförd av SCA</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2239,10 +2219,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126836451</v>
+        <v>126836260</v>
       </c>
       <c r="B17" t="n">
-        <v>79011</v>
+        <v>57657</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2250,34 +2230,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>680864</v>
+        <v>680809</v>
       </c>
       <c r="R17" t="n">
-        <v>7087091</v>
+        <v>7087061</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2310,6 +2295,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran) intill djupa körspår efter illegal avverkning genomförd av SCA</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2340,10 +2330,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126836465</v>
+        <v>126836258</v>
       </c>
       <c r="B18" t="n">
-        <v>79011</v>
+        <v>57657</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2351,34 +2341,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>680782</v>
+        <v>680805</v>
       </c>
       <c r="R18" t="n">
-        <v>7087268</v>
+        <v>7087122</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2411,6 +2406,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran) intill djupa körspår efter illegal avverkning genomförd av SCA</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2441,32 +2441,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126836282</v>
+        <v>126836452</v>
       </c>
       <c r="B19" t="n">
-        <v>80142</v>
+        <v>79014</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2476,10 +2476,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>680867</v>
+        <v>680856</v>
       </c>
       <c r="R19" t="n">
-        <v>7087092</v>
+        <v>7087078</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2542,32 +2542,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126836452</v>
+        <v>126836282</v>
       </c>
       <c r="B20" t="n">
-        <v>79011</v>
+        <v>80145</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2577,10 +2577,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>680856</v>
+        <v>680867</v>
       </c>
       <c r="R20" t="n">
-        <v>7087078</v>
+        <v>7087092</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2747,7 +2747,7 @@
         <v>126839980</v>
       </c>
       <c r="B22" t="n">
-        <v>75120</v>
+        <v>75123</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2845,45 +2845,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126838808</v>
+        <v>126836454</v>
       </c>
       <c r="B23" t="n">
-        <v>58027</v>
+        <v>79014</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Röjdtjärnviden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>680797</v>
+        <v>680813</v>
       </c>
       <c r="R23" t="n">
-        <v>7087093</v>
+        <v>7087014</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2930,12 +2930,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -2946,45 +2946,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126836454</v>
+        <v>126838808</v>
       </c>
       <c r="B24" t="n">
-        <v>79011</v>
+        <v>58027</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Röjdtjärnviden, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>680813</v>
+        <v>680797</v>
       </c>
       <c r="R24" t="n">
-        <v>7087014</v>
+        <v>7087093</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3031,12 +3031,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3047,45 +3047,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126836283</v>
+        <v>126840775</v>
       </c>
       <c r="B25" t="n">
-        <v>80142</v>
+        <v>78681</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6461</v>
+        <v>353</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Lämkullen, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>680788</v>
+        <v>680905</v>
       </c>
       <c r="R25" t="n">
-        <v>7087194</v>
+        <v>7087125</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3115,29 +3118,40 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3148,48 +3162,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126840775</v>
+        <v>126836283</v>
       </c>
       <c r="B26" t="n">
-        <v>78678</v>
+        <v>80145</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>353</v>
+        <v>6461</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Lämkullen, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>680905</v>
+        <v>680788</v>
       </c>
       <c r="R26" t="n">
-        <v>7087125</v>
+        <v>7087194</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3219,40 +3230,29 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>11:49</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>11:49</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3263,27 +3263,27 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126826864</v>
+        <v>126836456</v>
       </c>
       <c r="B27" t="n">
-        <v>80149</v>
+        <v>79014</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3294,14 +3294,14 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Slagörkullen, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>680792</v>
+        <v>680813</v>
       </c>
       <c r="R27" t="n">
-        <v>7087098</v>
+        <v>7087134</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3331,19 +3331,9 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>11:15</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>11:15</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3358,12 +3348,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3374,32 +3364,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126836456</v>
+        <v>126836223</v>
       </c>
       <c r="B28" t="n">
-        <v>79011</v>
+        <v>91290</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3409,10 +3399,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>680813</v>
+        <v>680802</v>
       </c>
       <c r="R28" t="n">
-        <v>7087134</v>
+        <v>7087182</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3475,10 +3465,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126836223</v>
+        <v>126826864</v>
       </c>
       <c r="B29" t="n">
-        <v>91284</v>
+        <v>80152</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3486,34 +3476,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5447</v>
+        <v>6463</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Slagörkullen, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>680802</v>
+        <v>680792</v>
       </c>
       <c r="R29" t="n">
-        <v>7087182</v>
+        <v>7087098</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3543,9 +3533,19 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3560,12 +3560,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3579,7 +3579,7 @@
         <v>126839926</v>
       </c>
       <c r="B30" t="n">
-        <v>75135</v>
+        <v>75138</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>126836448</v>
       </c>
       <c r="B31" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3778,32 +3778,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126836239</v>
+        <v>126836457</v>
       </c>
       <c r="B32" t="n">
-        <v>80143</v>
+        <v>79014</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3813,10 +3813,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>680791</v>
+        <v>680830</v>
       </c>
       <c r="R32" t="n">
-        <v>7087100</v>
+        <v>7087203</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3882,7 +3882,7 @@
         <v>126836277</v>
       </c>
       <c r="B33" t="n">
-        <v>97314</v>
+        <v>97320</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3980,32 +3980,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126836457</v>
+        <v>126836239</v>
       </c>
       <c r="B34" t="n">
-        <v>79011</v>
+        <v>80146</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4015,10 +4015,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>680830</v>
+        <v>680791</v>
       </c>
       <c r="R34" t="n">
-        <v>7087203</v>
+        <v>7087100</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4186,7 +4186,7 @@
         <v>126836281</v>
       </c>
       <c r="B36" t="n">
-        <v>80142</v>
+        <v>80145</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4287,7 +4287,7 @@
         <v>126839965</v>
       </c>
       <c r="B37" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4388,7 +4388,7 @@
         <v>126836358</v>
       </c>
       <c r="B38" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4486,50 +4486,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126836263</v>
+        <v>126836247</v>
       </c>
       <c r="B39" t="n">
-        <v>57657</v>
+        <v>80021</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>680847</v>
+        <v>680772</v>
       </c>
       <c r="R39" t="n">
-        <v>7087070</v>
+        <v>7087294</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4566,7 +4561,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>äldre ringhack (gran)</t>
+          <t>På asplåga</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4597,45 +4592,50 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126836247</v>
+        <v>126836263</v>
       </c>
       <c r="B40" t="n">
-        <v>80018</v>
+        <v>57657</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>680772</v>
+        <v>680847</v>
       </c>
       <c r="R40" t="n">
-        <v>7087294</v>
+        <v>7087070</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På asplåga</t>
+          <t>äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4706,7 +4706,7 @@
         <v>126836359</v>
       </c>
       <c r="B41" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4807,7 +4807,7 @@
         <v>126836450</v>
       </c>
       <c r="B42" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4905,10 +4905,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126836265</v>
+        <v>126839966</v>
       </c>
       <c r="B43" t="n">
-        <v>57657</v>
+        <v>79632</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4916,39 +4916,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>680876</v>
+        <v>680908</v>
       </c>
       <c r="R43" t="n">
-        <v>7086899</v>
+        <v>7087111</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4983,11 +4978,6 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>färska ringhack (gran)</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5000,12 +4990,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5016,10 +5006,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126839966</v>
+        <v>126836265</v>
       </c>
       <c r="B44" t="n">
-        <v>79629</v>
+        <v>57657</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5027,34 +5017,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>680908</v>
+        <v>680876</v>
       </c>
       <c r="R44" t="n">
-        <v>7087111</v>
+        <v>7086899</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5089,6 +5084,11 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>färska ringhack (gran)</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5101,12 +5101,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5231,7 +5231,7 @@
         <v>126836540</v>
       </c>
       <c r="B46" t="n">
-        <v>78678</v>
+        <v>78681</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5332,7 +5332,7 @@
         <v>126836212</v>
       </c>
       <c r="B47" t="n">
-        <v>75135</v>
+        <v>75138</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5433,7 +5433,7 @@
         <v>126836453</v>
       </c>
       <c r="B48" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5642,10 +5642,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126837045</v>
+        <v>126839954</v>
       </c>
       <c r="B50" t="n">
-        <v>91319</v>
+        <v>57817</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5653,34 +5653,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>680812</v>
+        <v>680871</v>
       </c>
       <c r="R50" t="n">
-        <v>7086987</v>
+        <v>7087130</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5727,12 +5727,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -5743,10 +5743,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126839954</v>
+        <v>126837045</v>
       </c>
       <c r="B51" t="n">
-        <v>57817</v>
+        <v>91325</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5754,34 +5754,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>680871</v>
+        <v>680812</v>
       </c>
       <c r="R51" t="n">
-        <v>7087130</v>
+        <v>7086987</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5828,12 +5828,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -5847,7 +5847,7 @@
         <v>126836213</v>
       </c>
       <c r="B52" t="n">
-        <v>75135</v>
+        <v>75138</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5948,7 +5948,7 @@
         <v>126836276</v>
       </c>
       <c r="B53" t="n">
-        <v>97314</v>
+        <v>97320</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6049,7 +6049,7 @@
         <v>126838799</v>
       </c>
       <c r="B54" t="n">
-        <v>98457</v>
+        <v>98463</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 64501-2023 artfynd.xlsx
+++ b/artfynd/A 64501-2023 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126836238</v>
+        <v>126836222</v>
       </c>
       <c r="B2" t="n">
-        <v>57817</v>
+        <v>91290</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>680851</v>
+        <v>680864</v>
       </c>
       <c r="R2" t="n">
-        <v>7087009</v>
+        <v>7087088</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,32 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126836222</v>
+        <v>126839924</v>
       </c>
       <c r="B3" t="n">
-        <v>91290</v>
+        <v>75138</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>680864</v>
+        <v>680859</v>
       </c>
       <c r="R3" t="n">
-        <v>7087088</v>
+        <v>7087090</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,12 +861,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126839924</v>
+        <v>126836238</v>
       </c>
       <c r="B4" t="n">
-        <v>75138</v>
+        <v>57817</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>680859</v>
+        <v>680851</v>
       </c>
       <c r="R4" t="n">
-        <v>7087090</v>
+        <v>7087009</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -962,12 +962,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -978,10 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126836264</v>
+        <v>126836455</v>
       </c>
       <c r="B5" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -989,39 +989,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>680811</v>
+        <v>680796</v>
       </c>
       <c r="R5" t="n">
-        <v>7087049</v>
+        <v>7087097</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1054,11 +1049,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1089,7 +1079,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126836229</v>
+        <v>126836264</v>
       </c>
       <c r="B6" t="n">
         <v>57657</v>
@@ -1117,9 +1107,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1128,10 +1119,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>680850</v>
+        <v>680811</v>
       </c>
       <c r="R6" t="n">
-        <v>7087177</v>
+        <v>7087049</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1164,6 +1155,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1194,45 +1190,49 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126836243</v>
+        <v>126836229</v>
       </c>
       <c r="B7" t="n">
-        <v>98463</v>
+        <v>57657</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>680867</v>
+        <v>680850</v>
       </c>
       <c r="R7" t="n">
-        <v>7087092</v>
+        <v>7087177</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1295,32 +1295,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126839930</v>
+        <v>126836243</v>
       </c>
       <c r="B8" t="n">
-        <v>75138</v>
+        <v>98463</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>221952</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1330,10 +1330,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>680800</v>
+        <v>680867</v>
       </c>
       <c r="R8" t="n">
-        <v>7087070</v>
+        <v>7087092</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1380,12 +1380,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1396,10 +1396,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126836455</v>
+        <v>126839930</v>
       </c>
       <c r="B9" t="n">
-        <v>79014</v>
+        <v>75138</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1407,21 +1407,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>680796</v>
+        <v>680800</v>
       </c>
       <c r="R9" t="n">
-        <v>7087097</v>
+        <v>7087070</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1481,12 +1481,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1497,50 +1497,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126839943</v>
+        <v>126836248</v>
       </c>
       <c r="B10" t="n">
-        <v>57657</v>
+        <v>80021</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>680794</v>
+        <v>680890</v>
       </c>
       <c r="R10" t="n">
-        <v>7087085</v>
+        <v>7086899</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1587,12 +1582,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1603,7 +1598,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126836499</v>
+        <v>126839943</v>
       </c>
       <c r="B11" t="n">
         <v>57657</v>
@@ -1634,7 +1629,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1643,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>680839</v>
+        <v>680794</v>
       </c>
       <c r="R11" t="n">
-        <v>7087048</v>
+        <v>7087085</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1693,12 +1688,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1709,7 +1704,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126836500</v>
+        <v>126836499</v>
       </c>
       <c r="B12" t="n">
         <v>57657</v>
@@ -1749,10 +1744,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>680809</v>
+        <v>680839</v>
       </c>
       <c r="R12" t="n">
-        <v>7087115</v>
+        <v>7087048</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,45 +1810,50 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126836248</v>
+        <v>126836500</v>
       </c>
       <c r="B13" t="n">
-        <v>80021</v>
+        <v>57657</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>680890</v>
+        <v>680809</v>
       </c>
       <c r="R13" t="n">
-        <v>7086899</v>
+        <v>7087115</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1916,45 +1916,50 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126839925</v>
+        <v>126836260</v>
       </c>
       <c r="B14" t="n">
-        <v>75123</v>
+        <v>57657</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>306</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>680859</v>
+        <v>680809</v>
       </c>
       <c r="R14" t="n">
-        <v>7087090</v>
+        <v>7087061</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1989,6 +1994,11 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran) intill djupa körspår efter illegal avverkning genomförd av SCA</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2001,12 +2011,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2017,10 +2027,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126836451</v>
+        <v>126836258</v>
       </c>
       <c r="B15" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2028,34 +2038,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>680864</v>
+        <v>680805</v>
       </c>
       <c r="R15" t="n">
-        <v>7087091</v>
+        <v>7087122</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2088,6 +2103,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran) intill djupa körspår efter illegal avverkning genomförd av SCA</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2118,32 +2138,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126836465</v>
+        <v>126839925</v>
       </c>
       <c r="B16" t="n">
-        <v>79014</v>
+        <v>75123</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2153,10 +2173,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>680782</v>
+        <v>680859</v>
       </c>
       <c r="R16" t="n">
-        <v>7087268</v>
+        <v>7087090</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2203,12 +2223,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2219,10 +2239,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126836260</v>
+        <v>126836451</v>
       </c>
       <c r="B17" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2230,39 +2250,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>680809</v>
+        <v>680864</v>
       </c>
       <c r="R17" t="n">
-        <v>7087061</v>
+        <v>7087091</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2295,11 +2310,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran) intill djupa körspår efter illegal avverkning genomförd av SCA</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2330,10 +2340,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126836258</v>
+        <v>126836465</v>
       </c>
       <c r="B18" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2341,39 +2351,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>680805</v>
+        <v>680782</v>
       </c>
       <c r="R18" t="n">
-        <v>7087122</v>
+        <v>7087268</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2406,11 +2411,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran) intill djupa körspår efter illegal avverkning genomförd av SCA</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2441,32 +2441,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126836452</v>
+        <v>126840006</v>
       </c>
       <c r="B19" t="n">
-        <v>79014</v>
+        <v>8436</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>106554</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2476,10 +2476,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>680856</v>
+        <v>680902</v>
       </c>
       <c r="R19" t="n">
-        <v>7087078</v>
+        <v>7087115</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2526,12 +2526,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2542,32 +2542,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126836282</v>
+        <v>126836452</v>
       </c>
       <c r="B20" t="n">
-        <v>80145</v>
+        <v>79014</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2577,10 +2577,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>680867</v>
+        <v>680856</v>
       </c>
       <c r="R20" t="n">
-        <v>7087092</v>
+        <v>7087078</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2643,10 +2643,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126840006</v>
+        <v>126836282</v>
       </c>
       <c r="B21" t="n">
-        <v>8436</v>
+        <v>80145</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2654,21 +2654,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106554</v>
+        <v>6461</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2678,10 +2678,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>680902</v>
+        <v>680867</v>
       </c>
       <c r="R21" t="n">
-        <v>7087115</v>
+        <v>7087092</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2728,12 +2728,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -3047,48 +3047,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126840775</v>
+        <v>126836283</v>
       </c>
       <c r="B25" t="n">
-        <v>78681</v>
+        <v>80145</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>353</v>
+        <v>6461</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Lämkullen, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>680905</v>
+        <v>680788</v>
       </c>
       <c r="R25" t="n">
-        <v>7087125</v>
+        <v>7087194</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3118,40 +3115,29 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>11:49</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>11:49</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3162,45 +3148,48 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126836283</v>
+        <v>126840775</v>
       </c>
       <c r="B26" t="n">
-        <v>80145</v>
+        <v>78681</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6461</v>
+        <v>353</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Lämkullen, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>680788</v>
+        <v>680905</v>
       </c>
       <c r="R26" t="n">
-        <v>7087194</v>
+        <v>7087125</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3230,29 +3219,40 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3263,32 +3263,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126836456</v>
+        <v>126836223</v>
       </c>
       <c r="B27" t="n">
-        <v>79014</v>
+        <v>91290</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3298,10 +3298,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>680813</v>
+        <v>680802</v>
       </c>
       <c r="R27" t="n">
-        <v>7087134</v>
+        <v>7087182</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3364,32 +3364,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126836223</v>
+        <v>126836456</v>
       </c>
       <c r="B28" t="n">
-        <v>91290</v>
+        <v>79014</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3399,10 +3399,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>680802</v>
+        <v>680813</v>
       </c>
       <c r="R28" t="n">
-        <v>7087182</v>
+        <v>7087134</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3778,32 +3778,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126836457</v>
+        <v>126836277</v>
       </c>
       <c r="B32" t="n">
-        <v>79014</v>
+        <v>97320</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3813,10 +3813,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>680830</v>
+        <v>680850</v>
       </c>
       <c r="R32" t="n">
-        <v>7087203</v>
+        <v>7087177</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3879,32 +3879,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126836277</v>
+        <v>126836457</v>
       </c>
       <c r="B33" t="n">
-        <v>97320</v>
+        <v>79014</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3914,10 +3914,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>680850</v>
+        <v>680830</v>
       </c>
       <c r="R33" t="n">
-        <v>7087177</v>
+        <v>7087203</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4905,10 +4905,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126839966</v>
+        <v>126836266</v>
       </c>
       <c r="B43" t="n">
-        <v>79632</v>
+        <v>57657</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4916,34 +4916,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>680908</v>
+        <v>680870</v>
       </c>
       <c r="R43" t="n">
-        <v>7087111</v>
+        <v>7086922</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4978,6 +4983,11 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Färska ringhack på nyligen tillskapad högstubbe i samband med av SCA genomförd illegal avverkning</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -4990,12 +5000,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5117,10 +5127,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126836266</v>
+        <v>126839966</v>
       </c>
       <c r="B45" t="n">
-        <v>57657</v>
+        <v>79632</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5128,39 +5138,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>680870</v>
+        <v>680908</v>
       </c>
       <c r="R45" t="n">
-        <v>7086922</v>
+        <v>7087111</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5195,11 +5200,6 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Färska ringhack på nyligen tillskapad högstubbe i samband med av SCA genomförd illegal avverkning</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5212,12 +5212,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">

--- a/artfynd/A 64501-2023 artfynd.xlsx
+++ b/artfynd/A 64501-2023 artfynd.xlsx
@@ -2441,10 +2441,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126840006</v>
+        <v>126836282</v>
       </c>
       <c r="B19" t="n">
-        <v>8436</v>
+        <v>80145</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2452,21 +2452,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106554</v>
+        <v>6461</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2476,10 +2476,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>680902</v>
+        <v>680867</v>
       </c>
       <c r="R19" t="n">
-        <v>7087115</v>
+        <v>7087092</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2526,12 +2526,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2542,32 +2542,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126836452</v>
+        <v>126840006</v>
       </c>
       <c r="B20" t="n">
-        <v>79014</v>
+        <v>8436</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>106554</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2577,10 +2577,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>680856</v>
+        <v>680902</v>
       </c>
       <c r="R20" t="n">
-        <v>7087078</v>
+        <v>7087115</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2627,12 +2627,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2643,32 +2643,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126836282</v>
+        <v>126836452</v>
       </c>
       <c r="B21" t="n">
-        <v>80145</v>
+        <v>79014</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2678,10 +2678,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>680867</v>
+        <v>680856</v>
       </c>
       <c r="R21" t="n">
-        <v>7087092</v>
+        <v>7087078</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3047,45 +3047,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126836283</v>
+        <v>126840775</v>
       </c>
       <c r="B25" t="n">
-        <v>80145</v>
+        <v>78681</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6461</v>
+        <v>353</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Lämkullen, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>680788</v>
+        <v>680905</v>
       </c>
       <c r="R25" t="n">
-        <v>7087194</v>
+        <v>7087125</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3115,29 +3118,40 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3148,48 +3162,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126840775</v>
+        <v>126836283</v>
       </c>
       <c r="B26" t="n">
-        <v>78681</v>
+        <v>80145</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>353</v>
+        <v>6461</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Lämkullen, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>680905</v>
+        <v>680788</v>
       </c>
       <c r="R26" t="n">
-        <v>7087125</v>
+        <v>7087194</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3219,40 +3230,29 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>11:49</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>11:49</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3263,32 +3263,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126836223</v>
+        <v>126836456</v>
       </c>
       <c r="B27" t="n">
-        <v>91290</v>
+        <v>79014</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3298,10 +3298,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>680802</v>
+        <v>680813</v>
       </c>
       <c r="R27" t="n">
-        <v>7087182</v>
+        <v>7087134</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3364,27 +3364,27 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126836456</v>
+        <v>126826864</v>
       </c>
       <c r="B28" t="n">
-        <v>79014</v>
+        <v>80152</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3395,14 +3395,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Slagörkullen, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>680813</v>
+        <v>680792</v>
       </c>
       <c r="R28" t="n">
-        <v>7087134</v>
+        <v>7087098</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3432,9 +3432,19 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3449,12 +3459,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3465,10 +3475,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126826864</v>
+        <v>126836223</v>
       </c>
       <c r="B29" t="n">
-        <v>80152</v>
+        <v>91290</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3476,34 +3486,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6463</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Slagörkullen, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>680792</v>
+        <v>680802</v>
       </c>
       <c r="R29" t="n">
-        <v>7087098</v>
+        <v>7087182</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3533,19 +3543,9 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>11:15</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>11:15</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3560,12 +3560,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3778,32 +3778,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126836277</v>
+        <v>126836457</v>
       </c>
       <c r="B32" t="n">
-        <v>97320</v>
+        <v>79014</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3813,10 +3813,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>680850</v>
+        <v>680830</v>
       </c>
       <c r="R32" t="n">
-        <v>7087177</v>
+        <v>7087203</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3879,32 +3879,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126836457</v>
+        <v>126836239</v>
       </c>
       <c r="B33" t="n">
-        <v>79014</v>
+        <v>80146</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3914,10 +3914,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>680830</v>
+        <v>680791</v>
       </c>
       <c r="R33" t="n">
-        <v>7087203</v>
+        <v>7087100</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3980,10 +3980,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126836239</v>
+        <v>126836277</v>
       </c>
       <c r="B34" t="n">
-        <v>80146</v>
+        <v>97320</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3991,21 +3991,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6462</v>
+        <v>221945</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4015,10 +4015,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>680791</v>
+        <v>680850</v>
       </c>
       <c r="R34" t="n">
-        <v>7087100</v>
+        <v>7087177</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -5329,10 +5329,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126836212</v>
+        <v>126836453</v>
       </c>
       <c r="B47" t="n">
-        <v>75138</v>
+        <v>79014</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5340,21 +5340,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5364,10 +5364,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>680844</v>
+        <v>680855</v>
       </c>
       <c r="R47" t="n">
-        <v>7087067</v>
+        <v>7087023</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5430,10 +5430,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126836453</v>
+        <v>126836212</v>
       </c>
       <c r="B48" t="n">
-        <v>79014</v>
+        <v>75138</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5441,21 +5441,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5465,10 +5465,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>680855</v>
+        <v>680844</v>
       </c>
       <c r="R48" t="n">
-        <v>7087023</v>
+        <v>7087067</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>

--- a/artfynd/A 64501-2023 artfynd.xlsx
+++ b/artfynd/A 64501-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126836222</v>
       </c>
       <c r="B2" t="n">
-        <v>91290</v>
+        <v>91291</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1079,10 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126836264</v>
+        <v>126839930</v>
       </c>
       <c r="B6" t="n">
-        <v>57657</v>
+        <v>75138</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,39 +1090,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>680811</v>
+        <v>680800</v>
       </c>
       <c r="R6" t="n">
-        <v>7087049</v>
+        <v>7087070</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1157,11 +1152,6 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>äldre ringhack (gran)</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1174,12 +1164,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1190,49 +1180,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126836229</v>
+        <v>126836243</v>
       </c>
       <c r="B7" t="n">
-        <v>57657</v>
+        <v>98464</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>680850</v>
+        <v>680867</v>
       </c>
       <c r="R7" t="n">
-        <v>7087177</v>
+        <v>7087092</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1295,45 +1281,50 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126836243</v>
+        <v>126836264</v>
       </c>
       <c r="B8" t="n">
-        <v>98463</v>
+        <v>57657</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>680867</v>
+        <v>680811</v>
       </c>
       <c r="R8" t="n">
-        <v>7087092</v>
+        <v>7087049</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1366,6 +1357,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1396,10 +1392,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126839930</v>
+        <v>126836229</v>
       </c>
       <c r="B9" t="n">
-        <v>75138</v>
+        <v>57657</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1407,34 +1403,38 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>680800</v>
+        <v>680850</v>
       </c>
       <c r="R9" t="n">
-        <v>7087070</v>
+        <v>7087177</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1481,12 +1481,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1916,50 +1916,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126836260</v>
+        <v>126839925</v>
       </c>
       <c r="B14" t="n">
-        <v>57657</v>
+        <v>75123</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>680809</v>
+        <v>680859</v>
       </c>
       <c r="R14" t="n">
-        <v>7087061</v>
+        <v>7087090</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1994,11 +1989,6 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran) intill djupa körspår efter illegal avverkning genomförd av SCA</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2011,12 +2001,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2027,10 +2017,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126836258</v>
+        <v>126836465</v>
       </c>
       <c r="B15" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2038,39 +2028,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>680805</v>
+        <v>680782</v>
       </c>
       <c r="R15" t="n">
-        <v>7087122</v>
+        <v>7087268</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,11 +2088,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran) intill djupa körspår efter illegal avverkning genomförd av SCA</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2138,32 +2118,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126839925</v>
+        <v>126836451</v>
       </c>
       <c r="B16" t="n">
-        <v>75123</v>
+        <v>79014</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>306</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2173,10 +2153,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>680859</v>
+        <v>680864</v>
       </c>
       <c r="R16" t="n">
-        <v>7087090</v>
+        <v>7087091</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2223,12 +2203,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2239,10 +2219,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126836451</v>
+        <v>126836260</v>
       </c>
       <c r="B17" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2250,34 +2230,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>680864</v>
+        <v>680809</v>
       </c>
       <c r="R17" t="n">
-        <v>7087091</v>
+        <v>7087061</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2310,6 +2295,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran) intill djupa körspår efter illegal avverkning genomförd av SCA</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2340,10 +2330,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126836465</v>
+        <v>126836258</v>
       </c>
       <c r="B18" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2351,34 +2341,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>680782</v>
+        <v>680805</v>
       </c>
       <c r="R18" t="n">
-        <v>7087268</v>
+        <v>7087122</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2411,6 +2406,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran) intill djupa körspår efter illegal avverkning genomförd av SCA</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2441,32 +2441,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126836282</v>
+        <v>126836452</v>
       </c>
       <c r="B19" t="n">
-        <v>80145</v>
+        <v>79014</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2476,10 +2476,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>680867</v>
+        <v>680856</v>
       </c>
       <c r="R19" t="n">
-        <v>7087092</v>
+        <v>7087078</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2542,10 +2542,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126840006</v>
+        <v>126836282</v>
       </c>
       <c r="B20" t="n">
-        <v>8436</v>
+        <v>80145</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2553,21 +2553,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106554</v>
+        <v>6461</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2577,10 +2577,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>680902</v>
+        <v>680867</v>
       </c>
       <c r="R20" t="n">
-        <v>7087115</v>
+        <v>7087092</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2627,12 +2627,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2643,32 +2643,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126836452</v>
+        <v>126840006</v>
       </c>
       <c r="B21" t="n">
-        <v>79014</v>
+        <v>8436</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>106554</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2678,10 +2678,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>680856</v>
+        <v>680902</v>
       </c>
       <c r="R21" t="n">
-        <v>7087078</v>
+        <v>7087115</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2728,12 +2728,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2845,45 +2845,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126836454</v>
+        <v>126838808</v>
       </c>
       <c r="B23" t="n">
-        <v>79014</v>
+        <v>58027</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Röjdtjärnviden, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>680813</v>
+        <v>680797</v>
       </c>
       <c r="R23" t="n">
-        <v>7087014</v>
+        <v>7087093</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2930,12 +2930,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -2946,45 +2946,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126838808</v>
+        <v>126836454</v>
       </c>
       <c r="B24" t="n">
-        <v>58027</v>
+        <v>79014</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Röjdtjärnviden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>680797</v>
+        <v>680813</v>
       </c>
       <c r="R24" t="n">
-        <v>7087093</v>
+        <v>7087014</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3031,12 +3031,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3047,48 +3047,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126840775</v>
+        <v>126836283</v>
       </c>
       <c r="B25" t="n">
-        <v>78681</v>
+        <v>80145</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>353</v>
+        <v>6461</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Lämkullen, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>680905</v>
+        <v>680788</v>
       </c>
       <c r="R25" t="n">
-        <v>7087125</v>
+        <v>7087194</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3118,40 +3115,29 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>11:49</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>11:49</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3162,45 +3148,48 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126836283</v>
+        <v>126840775</v>
       </c>
       <c r="B26" t="n">
-        <v>80145</v>
+        <v>78681</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6461</v>
+        <v>353</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Lämkullen, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>680788</v>
+        <v>680905</v>
       </c>
       <c r="R26" t="n">
-        <v>7087194</v>
+        <v>7087125</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3230,29 +3219,40 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3263,32 +3263,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126836456</v>
+        <v>126836223</v>
       </c>
       <c r="B27" t="n">
-        <v>79014</v>
+        <v>91291</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3298,10 +3298,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>680813</v>
+        <v>680802</v>
       </c>
       <c r="R27" t="n">
-        <v>7087134</v>
+        <v>7087182</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3364,27 +3364,27 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126826864</v>
+        <v>126836456</v>
       </c>
       <c r="B28" t="n">
-        <v>80152</v>
+        <v>79014</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3395,14 +3395,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Slagörkullen, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>680792</v>
+        <v>680813</v>
       </c>
       <c r="R28" t="n">
-        <v>7087098</v>
+        <v>7087134</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3432,19 +3432,9 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>11:15</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>11:15</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3459,12 +3449,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3475,10 +3465,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126836223</v>
+        <v>126826864</v>
       </c>
       <c r="B29" t="n">
-        <v>91290</v>
+        <v>80152</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3486,34 +3476,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5447</v>
+        <v>6463</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Slagörkullen, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>680802</v>
+        <v>680792</v>
       </c>
       <c r="R29" t="n">
-        <v>7087182</v>
+        <v>7087098</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3543,9 +3533,19 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3560,12 +3560,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3576,10 +3576,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126839926</v>
+        <v>126836448</v>
       </c>
       <c r="B30" t="n">
-        <v>75138</v>
+        <v>79014</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3587,21 +3587,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3611,10 +3611,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>680847</v>
+        <v>680910</v>
       </c>
       <c r="R30" t="n">
-        <v>7087085</v>
+        <v>7087135</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3661,12 +3661,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3677,10 +3677,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126836448</v>
+        <v>126839926</v>
       </c>
       <c r="B31" t="n">
-        <v>79014</v>
+        <v>75138</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3688,21 +3688,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3712,10 +3712,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>680910</v>
+        <v>680847</v>
       </c>
       <c r="R31" t="n">
-        <v>7087135</v>
+        <v>7087085</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3762,12 +3762,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3983,7 +3983,7 @@
         <v>126836277</v>
       </c>
       <c r="B34" t="n">
-        <v>97320</v>
+        <v>97321</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4905,10 +4905,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126836266</v>
+        <v>126839966</v>
       </c>
       <c r="B43" t="n">
-        <v>57657</v>
+        <v>79632</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4916,39 +4916,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>680870</v>
+        <v>680908</v>
       </c>
       <c r="R43" t="n">
-        <v>7086922</v>
+        <v>7087111</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4983,11 +4978,6 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Färska ringhack på nyligen tillskapad högstubbe i samband med av SCA genomförd illegal avverkning</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5000,12 +4990,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5016,7 +5006,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126836265</v>
+        <v>126836266</v>
       </c>
       <c r="B44" t="n">
         <v>57657</v>
@@ -5056,10 +5046,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>680876</v>
+        <v>680870</v>
       </c>
       <c r="R44" t="n">
-        <v>7086899</v>
+        <v>7086922</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5096,7 +5086,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>färska ringhack (gran)</t>
+          <t>Färska ringhack på nyligen tillskapad högstubbe i samband med av SCA genomförd illegal avverkning</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5127,10 +5117,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126839966</v>
+        <v>126836265</v>
       </c>
       <c r="B45" t="n">
-        <v>79632</v>
+        <v>57657</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5138,34 +5128,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>680908</v>
+        <v>680876</v>
       </c>
       <c r="R45" t="n">
-        <v>7087111</v>
+        <v>7086899</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5200,6 +5195,11 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>färska ringhack (gran)</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5212,12 +5212,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5642,10 +5642,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126839954</v>
+        <v>126836213</v>
       </c>
       <c r="B50" t="n">
-        <v>57817</v>
+        <v>75138</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5653,21 +5653,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103021</v>
+        <v>6440</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5677,10 +5677,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>680871</v>
+        <v>680800</v>
       </c>
       <c r="R50" t="n">
-        <v>7087130</v>
+        <v>7087109</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5727,12 +5727,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -5746,7 +5746,7 @@
         <v>126837045</v>
       </c>
       <c r="B51" t="n">
-        <v>91325</v>
+        <v>91326</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5844,10 +5844,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126836213</v>
+        <v>126839954</v>
       </c>
       <c r="B52" t="n">
-        <v>75138</v>
+        <v>57817</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5855,21 +5855,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6440</v>
+        <v>103021</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5879,10 +5879,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>680800</v>
+        <v>680871</v>
       </c>
       <c r="R52" t="n">
-        <v>7087109</v>
+        <v>7087130</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5929,12 +5929,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -5948,7 +5948,7 @@
         <v>126836276</v>
       </c>
       <c r="B53" t="n">
-        <v>97320</v>
+        <v>97321</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6049,7 +6049,7 @@
         <v>126838799</v>
       </c>
       <c r="B54" t="n">
-        <v>98463</v>
+        <v>98464</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 64501-2023 artfynd.xlsx
+++ b/artfynd/A 64501-2023 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126836222</v>
+        <v>126836238</v>
       </c>
       <c r="B2" t="n">
-        <v>91291</v>
+        <v>57817</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>680864</v>
+        <v>680851</v>
       </c>
       <c r="R2" t="n">
-        <v>7087088</v>
+        <v>7087009</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,32 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126839924</v>
+        <v>126836222</v>
       </c>
       <c r="B3" t="n">
-        <v>75138</v>
+        <v>91291</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>680859</v>
+        <v>680864</v>
       </c>
       <c r="R3" t="n">
-        <v>7087090</v>
+        <v>7087088</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,12 +861,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126836238</v>
+        <v>126839924</v>
       </c>
       <c r="B4" t="n">
-        <v>57817</v>
+        <v>75138</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>6440</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>680851</v>
+        <v>680859</v>
       </c>
       <c r="R4" t="n">
-        <v>7087009</v>
+        <v>7087090</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -962,12 +962,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1497,45 +1497,50 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126836248</v>
+        <v>126839943</v>
       </c>
       <c r="B10" t="n">
-        <v>80021</v>
+        <v>57657</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>680890</v>
+        <v>680794</v>
       </c>
       <c r="R10" t="n">
-        <v>7086899</v>
+        <v>7087085</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1582,12 +1587,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1598,7 +1603,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126839943</v>
+        <v>126836499</v>
       </c>
       <c r="B11" t="n">
         <v>57657</v>
@@ -1629,7 +1634,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1638,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>680794</v>
+        <v>680839</v>
       </c>
       <c r="R11" t="n">
-        <v>7087085</v>
+        <v>7087048</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1688,12 +1693,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1704,7 +1709,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126836499</v>
+        <v>126836500</v>
       </c>
       <c r="B12" t="n">
         <v>57657</v>
@@ -1744,10 +1749,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>680839</v>
+        <v>680809</v>
       </c>
       <c r="R12" t="n">
-        <v>7087048</v>
+        <v>7087115</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1810,50 +1815,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126836500</v>
+        <v>126836248</v>
       </c>
       <c r="B13" t="n">
-        <v>57657</v>
+        <v>80021</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>680809</v>
+        <v>680890</v>
       </c>
       <c r="R13" t="n">
-        <v>7087115</v>
+        <v>7086899</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -3047,45 +3047,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126836283</v>
+        <v>126840775</v>
       </c>
       <c r="B25" t="n">
-        <v>80145</v>
+        <v>78681</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6461</v>
+        <v>353</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Lämkullen, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>680788</v>
+        <v>680905</v>
       </c>
       <c r="R25" t="n">
-        <v>7087194</v>
+        <v>7087125</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3115,29 +3118,40 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3148,48 +3162,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126840775</v>
+        <v>126836283</v>
       </c>
       <c r="B26" t="n">
-        <v>78681</v>
+        <v>80145</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>353</v>
+        <v>6461</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Lämkullen, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>680905</v>
+        <v>680788</v>
       </c>
       <c r="R26" t="n">
-        <v>7087125</v>
+        <v>7087194</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3219,40 +3230,29 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>11:49</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>11:49</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -5329,10 +5329,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126836453</v>
+        <v>126836267</v>
       </c>
       <c r="B47" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5340,34 +5340,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>680855</v>
+        <v>680851</v>
       </c>
       <c r="R47" t="n">
-        <v>7087023</v>
+        <v>7087171</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5400,6 +5405,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5430,10 +5440,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126836212</v>
+        <v>126836453</v>
       </c>
       <c r="B48" t="n">
-        <v>75138</v>
+        <v>79014</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5441,21 +5451,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5465,10 +5475,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>680844</v>
+        <v>680855</v>
       </c>
       <c r="R48" t="n">
-        <v>7087067</v>
+        <v>7087023</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5531,10 +5541,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126836267</v>
+        <v>126836212</v>
       </c>
       <c r="B49" t="n">
-        <v>57657</v>
+        <v>75138</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5542,39 +5552,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>680851</v>
+        <v>680844</v>
       </c>
       <c r="R49" t="n">
-        <v>7087171</v>
+        <v>7087067</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5607,11 +5612,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD49" t="b">

--- a/artfynd/A 64501-2023 artfynd.xlsx
+++ b/artfynd/A 64501-2023 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126836238</v>
+        <v>126836222</v>
       </c>
       <c r="B2" t="n">
-        <v>57817</v>
+        <v>91291</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>680851</v>
+        <v>680864</v>
       </c>
       <c r="R2" t="n">
-        <v>7087009</v>
+        <v>7087088</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,32 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126836222</v>
+        <v>126836238</v>
       </c>
       <c r="B3" t="n">
-        <v>91291</v>
+        <v>57817</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>680864</v>
+        <v>680851</v>
       </c>
       <c r="R3" t="n">
-        <v>7087088</v>
+        <v>7087009</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1079,10 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126839930</v>
+        <v>126836264</v>
       </c>
       <c r="B6" t="n">
-        <v>75138</v>
+        <v>57657</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,34 +1090,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>680800</v>
+        <v>680811</v>
       </c>
       <c r="R6" t="n">
-        <v>7087070</v>
+        <v>7087049</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1152,6 +1157,11 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>äldre ringhack (gran)</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1164,12 +1174,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1180,45 +1190,49 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126836243</v>
+        <v>126836229</v>
       </c>
       <c r="B7" t="n">
-        <v>98464</v>
+        <v>57657</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>680867</v>
+        <v>680850</v>
       </c>
       <c r="R7" t="n">
-        <v>7087092</v>
+        <v>7087177</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,50 +1295,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126836264</v>
+        <v>126836243</v>
       </c>
       <c r="B8" t="n">
-        <v>57657</v>
+        <v>98464</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>680811</v>
+        <v>680867</v>
       </c>
       <c r="R8" t="n">
-        <v>7087049</v>
+        <v>7087092</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1357,11 +1366,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1392,10 +1396,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126836229</v>
+        <v>126839930</v>
       </c>
       <c r="B9" t="n">
-        <v>57657</v>
+        <v>75138</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1403,38 +1407,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>680850</v>
+        <v>680800</v>
       </c>
       <c r="R9" t="n">
-        <v>7087177</v>
+        <v>7087070</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1481,12 +1481,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1916,45 +1916,50 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126839925</v>
+        <v>126836260</v>
       </c>
       <c r="B14" t="n">
-        <v>75123</v>
+        <v>57657</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>306</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>680859</v>
+        <v>680809</v>
       </c>
       <c r="R14" t="n">
-        <v>7087090</v>
+        <v>7087061</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1989,6 +1994,11 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran) intill djupa körspår efter illegal avverkning genomförd av SCA</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2001,12 +2011,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2017,10 +2027,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126836465</v>
+        <v>126836258</v>
       </c>
       <c r="B15" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2028,34 +2038,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>680782</v>
+        <v>680805</v>
       </c>
       <c r="R15" t="n">
-        <v>7087268</v>
+        <v>7087122</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2088,6 +2103,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran) intill djupa körspår efter illegal avverkning genomförd av SCA</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2219,10 +2239,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126836260</v>
+        <v>126836465</v>
       </c>
       <c r="B17" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2230,39 +2250,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>680809</v>
+        <v>680782</v>
       </c>
       <c r="R17" t="n">
-        <v>7087061</v>
+        <v>7087268</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2295,11 +2310,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran) intill djupa körspår efter illegal avverkning genomförd av SCA</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2330,50 +2340,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126836258</v>
+        <v>126839925</v>
       </c>
       <c r="B18" t="n">
-        <v>57657</v>
+        <v>75123</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>680805</v>
+        <v>680859</v>
       </c>
       <c r="R18" t="n">
-        <v>7087122</v>
+        <v>7087090</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2408,11 +2413,6 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran) intill djupa körspår efter illegal avverkning genomförd av SCA</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2425,12 +2425,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2441,32 +2441,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126836452</v>
+        <v>126836282</v>
       </c>
       <c r="B19" t="n">
-        <v>79014</v>
+        <v>80145</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2476,10 +2476,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>680856</v>
+        <v>680867</v>
       </c>
       <c r="R19" t="n">
-        <v>7087078</v>
+        <v>7087092</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2542,32 +2542,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126836282</v>
+        <v>126836452</v>
       </c>
       <c r="B20" t="n">
-        <v>80145</v>
+        <v>79014</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2577,10 +2577,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>680867</v>
+        <v>680856</v>
       </c>
       <c r="R20" t="n">
-        <v>7087092</v>
+        <v>7087078</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2744,32 +2744,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126839980</v>
+        <v>126836454</v>
       </c>
       <c r="B22" t="n">
-        <v>75123</v>
+        <v>79014</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>306</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>680796</v>
+        <v>680813</v>
       </c>
       <c r="R22" t="n">
-        <v>7087081</v>
+        <v>7087014</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2829,12 +2829,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2845,10 +2845,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126838808</v>
+        <v>126839980</v>
       </c>
       <c r="B23" t="n">
-        <v>58027</v>
+        <v>75123</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2856,34 +2856,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103015</v>
+        <v>306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Röjdtjärnviden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>680797</v>
+        <v>680796</v>
       </c>
       <c r="R23" t="n">
-        <v>7087093</v>
+        <v>7087081</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2930,12 +2930,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -2946,45 +2946,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126836454</v>
+        <v>126838808</v>
       </c>
       <c r="B24" t="n">
-        <v>79014</v>
+        <v>58027</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Röjdtjärnviden, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>680813</v>
+        <v>680797</v>
       </c>
       <c r="R24" t="n">
-        <v>7087014</v>
+        <v>7087093</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3031,12 +3031,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3047,48 +3047,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126840775</v>
+        <v>126836283</v>
       </c>
       <c r="B25" t="n">
-        <v>78681</v>
+        <v>80145</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>353</v>
+        <v>6461</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Lämkullen, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>680905</v>
+        <v>680788</v>
       </c>
       <c r="R25" t="n">
-        <v>7087125</v>
+        <v>7087194</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3118,40 +3115,29 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>11:49</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>11:49</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3162,45 +3148,48 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126836283</v>
+        <v>126840775</v>
       </c>
       <c r="B26" t="n">
-        <v>80145</v>
+        <v>78681</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6461</v>
+        <v>353</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Lämkullen, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>680788</v>
+        <v>680905</v>
       </c>
       <c r="R26" t="n">
-        <v>7087194</v>
+        <v>7087125</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3230,29 +3219,40 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3364,27 +3364,27 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126836456</v>
+        <v>126826864</v>
       </c>
       <c r="B28" t="n">
-        <v>79014</v>
+        <v>80152</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3395,14 +3395,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Slagörkullen, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>680813</v>
+        <v>680792</v>
       </c>
       <c r="R28" t="n">
-        <v>7087134</v>
+        <v>7087098</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3432,9 +3432,19 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3449,12 +3459,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3465,27 +3475,27 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126826864</v>
+        <v>126836456</v>
       </c>
       <c r="B29" t="n">
-        <v>80152</v>
+        <v>79014</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3496,14 +3506,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Slagörkullen, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>680792</v>
+        <v>680813</v>
       </c>
       <c r="R29" t="n">
-        <v>7087098</v>
+        <v>7087134</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3533,19 +3543,9 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>11:15</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>11:15</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3560,12 +3560,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3576,10 +3576,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126836448</v>
+        <v>126839926</v>
       </c>
       <c r="B30" t="n">
-        <v>79014</v>
+        <v>75138</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3587,21 +3587,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3611,10 +3611,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>680910</v>
+        <v>680847</v>
       </c>
       <c r="R30" t="n">
-        <v>7087135</v>
+        <v>7087085</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3661,12 +3661,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3677,10 +3677,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126839926</v>
+        <v>126836448</v>
       </c>
       <c r="B31" t="n">
-        <v>75138</v>
+        <v>79014</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3688,21 +3688,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3712,10 +3712,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>680847</v>
+        <v>680910</v>
       </c>
       <c r="R31" t="n">
-        <v>7087085</v>
+        <v>7087135</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3762,12 +3762,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3778,32 +3778,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126836457</v>
+        <v>126836239</v>
       </c>
       <c r="B32" t="n">
-        <v>79014</v>
+        <v>80146</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3813,10 +3813,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>680830</v>
+        <v>680791</v>
       </c>
       <c r="R32" t="n">
-        <v>7087203</v>
+        <v>7087100</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3879,10 +3879,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126836239</v>
+        <v>126836277</v>
       </c>
       <c r="B33" t="n">
-        <v>80146</v>
+        <v>97321</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3890,21 +3890,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6462</v>
+        <v>221945</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3914,10 +3914,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>680791</v>
+        <v>680850</v>
       </c>
       <c r="R33" t="n">
-        <v>7087100</v>
+        <v>7087177</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3980,32 +3980,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126836277</v>
+        <v>126836457</v>
       </c>
       <c r="B34" t="n">
-        <v>97321</v>
+        <v>79014</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4015,10 +4015,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>680850</v>
+        <v>680830</v>
       </c>
       <c r="R34" t="n">
-        <v>7087177</v>
+        <v>7087203</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4385,32 +4385,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126836358</v>
+        <v>126836247</v>
       </c>
       <c r="B38" t="n">
-        <v>79014</v>
+        <v>80021</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4420,10 +4420,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>680811</v>
+        <v>680772</v>
       </c>
       <c r="R38" t="n">
-        <v>7086966</v>
+        <v>7087294</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4456,6 +4456,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>På asplåga</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4486,32 +4491,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126836247</v>
+        <v>126836358</v>
       </c>
       <c r="B39" t="n">
-        <v>80021</v>
+        <v>79014</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4521,10 +4526,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>680772</v>
+        <v>680811</v>
       </c>
       <c r="R39" t="n">
-        <v>7087294</v>
+        <v>7086966</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4557,11 +4562,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>På asplåga</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5440,10 +5440,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126836453</v>
+        <v>126836212</v>
       </c>
       <c r="B48" t="n">
-        <v>79014</v>
+        <v>75138</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5451,21 +5451,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5475,10 +5475,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>680855</v>
+        <v>680844</v>
       </c>
       <c r="R48" t="n">
-        <v>7087023</v>
+        <v>7087067</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5541,10 +5541,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126836212</v>
+        <v>126836453</v>
       </c>
       <c r="B49" t="n">
-        <v>75138</v>
+        <v>79014</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5552,21 +5552,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5576,10 +5576,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>680844</v>
+        <v>680855</v>
       </c>
       <c r="R49" t="n">
-        <v>7087067</v>
+        <v>7087023</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5642,10 +5642,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126836213</v>
+        <v>126837045</v>
       </c>
       <c r="B50" t="n">
-        <v>75138</v>
+        <v>91326</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5653,34 +5653,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>680800</v>
+        <v>680812</v>
       </c>
       <c r="R50" t="n">
-        <v>7087109</v>
+        <v>7086987</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5727,12 +5727,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -5743,10 +5743,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126837045</v>
+        <v>126839954</v>
       </c>
       <c r="B51" t="n">
-        <v>91326</v>
+        <v>57817</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5754,34 +5754,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>680812</v>
+        <v>680871</v>
       </c>
       <c r="R51" t="n">
-        <v>7086987</v>
+        <v>7087130</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5828,12 +5828,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -5844,10 +5844,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126839954</v>
+        <v>126836213</v>
       </c>
       <c r="B52" t="n">
-        <v>57817</v>
+        <v>75138</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5855,21 +5855,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103021</v>
+        <v>6440</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5879,10 +5879,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>680871</v>
+        <v>680800</v>
       </c>
       <c r="R52" t="n">
-        <v>7087130</v>
+        <v>7087109</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5929,12 +5929,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">

--- a/artfynd/A 64501-2023 artfynd.xlsx
+++ b/artfynd/A 64501-2023 artfynd.xlsx
@@ -1916,10 +1916,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126836260</v>
+        <v>126836451</v>
       </c>
       <c r="B14" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1927,39 +1927,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>680809</v>
+        <v>680864</v>
       </c>
       <c r="R14" t="n">
-        <v>7087061</v>
+        <v>7087091</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1992,11 +1987,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran) intill djupa körspår efter illegal avverkning genomförd av SCA</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2027,10 +2017,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126836258</v>
+        <v>126836465</v>
       </c>
       <c r="B15" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2038,39 +2028,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>680805</v>
+        <v>680782</v>
       </c>
       <c r="R15" t="n">
-        <v>7087122</v>
+        <v>7087268</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,11 +2088,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran) intill djupa körspår efter illegal avverkning genomförd av SCA</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2138,10 +2118,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126836451</v>
+        <v>126836260</v>
       </c>
       <c r="B16" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2149,34 +2129,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>680864</v>
+        <v>680809</v>
       </c>
       <c r="R16" t="n">
-        <v>7087091</v>
+        <v>7087061</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2209,6 +2194,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran) intill djupa körspår efter illegal avverkning genomförd av SCA</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2239,10 +2229,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126836465</v>
+        <v>126836258</v>
       </c>
       <c r="B17" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2250,34 +2240,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>680782</v>
+        <v>680805</v>
       </c>
       <c r="R17" t="n">
-        <v>7087268</v>
+        <v>7087122</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2310,6 +2305,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran) intill djupa körspår efter illegal avverkning genomförd av SCA</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -3047,45 +3047,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126836283</v>
+        <v>126840775</v>
       </c>
       <c r="B25" t="n">
-        <v>80145</v>
+        <v>78681</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6461</v>
+        <v>353</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Lämkullen, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>680788</v>
+        <v>680905</v>
       </c>
       <c r="R25" t="n">
-        <v>7087194</v>
+        <v>7087125</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3115,29 +3118,40 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3148,48 +3162,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126840775</v>
+        <v>126836283</v>
       </c>
       <c r="B26" t="n">
-        <v>78681</v>
+        <v>80145</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>353</v>
+        <v>6461</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Lämkullen, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>680905</v>
+        <v>680788</v>
       </c>
       <c r="R26" t="n">
-        <v>7087125</v>
+        <v>7087194</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3219,40 +3230,29 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>11:49</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>11:49</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3364,27 +3364,27 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126826864</v>
+        <v>126836456</v>
       </c>
       <c r="B28" t="n">
-        <v>80152</v>
+        <v>79014</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3395,14 +3395,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Slagörkullen, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>680792</v>
+        <v>680813</v>
       </c>
       <c r="R28" t="n">
-        <v>7087098</v>
+        <v>7087134</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3432,19 +3432,9 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>11:15</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>11:15</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3459,12 +3449,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3475,27 +3465,27 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126836456</v>
+        <v>126826864</v>
       </c>
       <c r="B29" t="n">
-        <v>79014</v>
+        <v>80152</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3506,14 +3496,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Slagörkullen, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>680813</v>
+        <v>680792</v>
       </c>
       <c r="R29" t="n">
-        <v>7087134</v>
+        <v>7087098</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3543,9 +3533,19 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3560,12 +3560,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3879,32 +3879,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126836277</v>
+        <v>126836457</v>
       </c>
       <c r="B33" t="n">
-        <v>97321</v>
+        <v>79014</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3914,10 +3914,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>680850</v>
+        <v>680830</v>
       </c>
       <c r="R33" t="n">
-        <v>7087177</v>
+        <v>7087203</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3980,32 +3980,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126836457</v>
+        <v>126836277</v>
       </c>
       <c r="B34" t="n">
-        <v>79014</v>
+        <v>97321</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4015,10 +4015,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>680830</v>
+        <v>680850</v>
       </c>
       <c r="R34" t="n">
-        <v>7087203</v>
+        <v>7087177</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -5642,10 +5642,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126837045</v>
+        <v>126836213</v>
       </c>
       <c r="B50" t="n">
-        <v>91326</v>
+        <v>75138</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5653,34 +5653,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>680812</v>
+        <v>680800</v>
       </c>
       <c r="R50" t="n">
-        <v>7086987</v>
+        <v>7087109</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5727,12 +5727,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -5743,10 +5743,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126839954</v>
+        <v>126837045</v>
       </c>
       <c r="B51" t="n">
-        <v>57817</v>
+        <v>91326</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5754,34 +5754,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>680871</v>
+        <v>680812</v>
       </c>
       <c r="R51" t="n">
-        <v>7087130</v>
+        <v>7086987</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5828,12 +5828,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -5844,10 +5844,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126836213</v>
+        <v>126839954</v>
       </c>
       <c r="B52" t="n">
-        <v>75138</v>
+        <v>57817</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5855,21 +5855,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6440</v>
+        <v>103021</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5879,10 +5879,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>680800</v>
+        <v>680871</v>
       </c>
       <c r="R52" t="n">
-        <v>7087109</v>
+        <v>7087130</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5929,12 +5929,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">

--- a/artfynd/A 64501-2023 artfynd.xlsx
+++ b/artfynd/A 64501-2023 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126836222</v>
+        <v>126839924</v>
       </c>
       <c r="B2" t="n">
-        <v>91291</v>
+        <v>75138</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>6440</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>680864</v>
+        <v>680859</v>
       </c>
       <c r="R2" t="n">
-        <v>7087088</v>
+        <v>7087090</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,12 +760,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -776,32 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126836238</v>
+        <v>126836222</v>
       </c>
       <c r="B3" t="n">
-        <v>57817</v>
+        <v>91291</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>680851</v>
+        <v>680864</v>
       </c>
       <c r="R3" t="n">
-        <v>7087009</v>
+        <v>7087088</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126839924</v>
+        <v>126836238</v>
       </c>
       <c r="B4" t="n">
-        <v>75138</v>
+        <v>57817</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>680859</v>
+        <v>680851</v>
       </c>
       <c r="R4" t="n">
-        <v>7087090</v>
+        <v>7087009</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -962,12 +962,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -978,10 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126836455</v>
+        <v>126839930</v>
       </c>
       <c r="B5" t="n">
-        <v>79014</v>
+        <v>75138</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -989,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>680796</v>
+        <v>680800</v>
       </c>
       <c r="R5" t="n">
-        <v>7087097</v>
+        <v>7087070</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,12 +1063,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1295,32 +1295,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126836243</v>
+        <v>126836455</v>
       </c>
       <c r="B8" t="n">
-        <v>98464</v>
+        <v>79014</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1330,10 +1330,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>680867</v>
+        <v>680796</v>
       </c>
       <c r="R8" t="n">
-        <v>7087092</v>
+        <v>7087097</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1396,32 +1396,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126839930</v>
+        <v>126836243</v>
       </c>
       <c r="B9" t="n">
-        <v>75138</v>
+        <v>98464</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>221952</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>680800</v>
+        <v>680867</v>
       </c>
       <c r="R9" t="n">
-        <v>7087070</v>
+        <v>7087092</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1481,12 +1481,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -2441,32 +2441,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126836282</v>
+        <v>126836452</v>
       </c>
       <c r="B19" t="n">
-        <v>80145</v>
+        <v>79014</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2476,10 +2476,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>680867</v>
+        <v>680856</v>
       </c>
       <c r="R19" t="n">
-        <v>7087092</v>
+        <v>7087078</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2542,32 +2542,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126836452</v>
+        <v>126836282</v>
       </c>
       <c r="B20" t="n">
-        <v>79014</v>
+        <v>80145</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2577,10 +2577,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>680856</v>
+        <v>680867</v>
       </c>
       <c r="R20" t="n">
-        <v>7087078</v>
+        <v>7087092</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -4385,32 +4385,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126836247</v>
+        <v>126836358</v>
       </c>
       <c r="B38" t="n">
-        <v>80021</v>
+        <v>79014</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4420,10 +4420,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>680772</v>
+        <v>680811</v>
       </c>
       <c r="R38" t="n">
-        <v>7087294</v>
+        <v>7086966</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4456,11 +4456,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>På asplåga</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4491,32 +4486,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126836358</v>
+        <v>126836247</v>
       </c>
       <c r="B39" t="n">
-        <v>79014</v>
+        <v>80021</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4526,10 +4521,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>680811</v>
+        <v>680772</v>
       </c>
       <c r="R39" t="n">
-        <v>7086966</v>
+        <v>7087294</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4562,6 +4557,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>På asplåga</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5329,10 +5329,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126836267</v>
+        <v>126836212</v>
       </c>
       <c r="B47" t="n">
-        <v>57657</v>
+        <v>75138</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5340,39 +5340,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>680851</v>
+        <v>680844</v>
       </c>
       <c r="R47" t="n">
-        <v>7087171</v>
+        <v>7087067</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5405,11 +5400,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5440,10 +5430,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126836212</v>
+        <v>126836453</v>
       </c>
       <c r="B48" t="n">
-        <v>75138</v>
+        <v>79014</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5451,21 +5441,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5475,10 +5465,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>680844</v>
+        <v>680855</v>
       </c>
       <c r="R48" t="n">
-        <v>7087067</v>
+        <v>7087023</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5541,10 +5531,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126836453</v>
+        <v>126836267</v>
       </c>
       <c r="B49" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5552,34 +5542,39 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>680855</v>
+        <v>680851</v>
       </c>
       <c r="R49" t="n">
-        <v>7087023</v>
+        <v>7087171</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5612,6 +5607,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD49" t="b">

--- a/artfynd/A 64501-2023 artfynd.xlsx
+++ b/artfynd/A 64501-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126839924</v>
       </c>
       <c r="B2" t="n">
-        <v>75138</v>
+        <v>75142</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -776,32 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126836222</v>
+        <v>126836238</v>
       </c>
       <c r="B3" t="n">
-        <v>91291</v>
+        <v>57821</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>680864</v>
+        <v>680851</v>
       </c>
       <c r="R3" t="n">
-        <v>7087088</v>
+        <v>7087009</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,32 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126836238</v>
+        <v>126836222</v>
       </c>
       <c r="B4" t="n">
-        <v>57817</v>
+        <v>91295</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>680851</v>
+        <v>680864</v>
       </c>
       <c r="R4" t="n">
-        <v>7087009</v>
+        <v>7087088</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,10 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126839930</v>
+        <v>126836455</v>
       </c>
       <c r="B5" t="n">
-        <v>75138</v>
+        <v>79018</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -989,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>680800</v>
+        <v>680796</v>
       </c>
       <c r="R5" t="n">
-        <v>7087070</v>
+        <v>7087097</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,12 +1063,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1079,10 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126836264</v>
+        <v>126839930</v>
       </c>
       <c r="B6" t="n">
-        <v>57657</v>
+        <v>75142</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,39 +1090,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>680811</v>
+        <v>680800</v>
       </c>
       <c r="R6" t="n">
-        <v>7087049</v>
+        <v>7087070</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1157,11 +1152,6 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>äldre ringhack (gran)</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1174,12 +1164,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1193,7 +1183,7 @@
         <v>126836229</v>
       </c>
       <c r="B7" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,10 +1285,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126836455</v>
+        <v>126836264</v>
       </c>
       <c r="B8" t="n">
-        <v>79014</v>
+        <v>57661</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1306,34 +1296,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>680796</v>
+        <v>680811</v>
       </c>
       <c r="R8" t="n">
-        <v>7087097</v>
+        <v>7087049</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1366,6 +1361,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1399,7 +1399,7 @@
         <v>126836243</v>
       </c>
       <c r="B9" t="n">
-        <v>98464</v>
+        <v>98468</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1497,50 +1497,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126839943</v>
+        <v>126836248</v>
       </c>
       <c r="B10" t="n">
-        <v>57657</v>
+        <v>80025</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>680794</v>
+        <v>680890</v>
       </c>
       <c r="R10" t="n">
-        <v>7087085</v>
+        <v>7086899</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1587,12 +1582,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1603,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126836499</v>
+        <v>126839943</v>
       </c>
       <c r="B11" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1634,7 +1629,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1643,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>680839</v>
+        <v>680794</v>
       </c>
       <c r="R11" t="n">
-        <v>7087048</v>
+        <v>7087085</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1693,12 +1688,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1709,10 +1704,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126836500</v>
+        <v>126836499</v>
       </c>
       <c r="B12" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1749,10 +1744,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>680809</v>
+        <v>680839</v>
       </c>
       <c r="R12" t="n">
-        <v>7087115</v>
+        <v>7087048</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,45 +1810,50 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126836248</v>
+        <v>126836500</v>
       </c>
       <c r="B13" t="n">
-        <v>80021</v>
+        <v>57661</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>680890</v>
+        <v>680809</v>
       </c>
       <c r="R13" t="n">
-        <v>7086899</v>
+        <v>7087115</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1916,32 +1916,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126836451</v>
+        <v>126839925</v>
       </c>
       <c r="B14" t="n">
-        <v>79014</v>
+        <v>75127</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1951,10 +1951,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>680864</v>
+        <v>680859</v>
       </c>
       <c r="R14" t="n">
-        <v>7087091</v>
+        <v>7087090</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,12 +2001,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2017,10 +2017,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126836465</v>
+        <v>126836451</v>
       </c>
       <c r="B15" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2052,10 +2052,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>680782</v>
+        <v>680864</v>
       </c>
       <c r="R15" t="n">
-        <v>7087268</v>
+        <v>7087091</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2118,10 +2118,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126836260</v>
+        <v>126836465</v>
       </c>
       <c r="B16" t="n">
-        <v>57657</v>
+        <v>79018</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2129,39 +2129,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>680809</v>
+        <v>680782</v>
       </c>
       <c r="R16" t="n">
-        <v>7087061</v>
+        <v>7087268</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2194,11 +2189,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran) intill djupa körspår efter illegal avverkning genomförd av SCA</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2229,10 +2219,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126836258</v>
+        <v>126836260</v>
       </c>
       <c r="B17" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2269,10 +2259,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>680805</v>
+        <v>680809</v>
       </c>
       <c r="R17" t="n">
-        <v>7087122</v>
+        <v>7087061</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2340,45 +2330,50 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126839925</v>
+        <v>126836258</v>
       </c>
       <c r="B18" t="n">
-        <v>75123</v>
+        <v>57661</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>306</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>680859</v>
+        <v>680805</v>
       </c>
       <c r="R18" t="n">
-        <v>7087090</v>
+        <v>7087122</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2413,6 +2408,11 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran) intill djupa körspår efter illegal avverkning genomförd av SCA</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2425,12 +2425,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2444,7 +2444,7 @@
         <v>126836452</v>
       </c>
       <c r="B19" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         <v>126836282</v>
       </c>
       <c r="B20" t="n">
-        <v>80145</v>
+        <v>80149</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2646,7 +2646,7 @@
         <v>126840006</v>
       </c>
       <c r="B21" t="n">
-        <v>8436</v>
+        <v>8439</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2744,32 +2744,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126836454</v>
+        <v>126839980</v>
       </c>
       <c r="B22" t="n">
-        <v>79014</v>
+        <v>75127</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>680813</v>
+        <v>680796</v>
       </c>
       <c r="R22" t="n">
-        <v>7087014</v>
+        <v>7087081</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2829,12 +2829,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2845,32 +2845,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126839980</v>
+        <v>126836454</v>
       </c>
       <c r="B23" t="n">
-        <v>75123</v>
+        <v>79018</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>306</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2880,10 +2880,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>680796</v>
+        <v>680813</v>
       </c>
       <c r="R23" t="n">
-        <v>7087081</v>
+        <v>7087014</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2930,12 +2930,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -2949,7 +2949,7 @@
         <v>126838808</v>
       </c>
       <c r="B24" t="n">
-        <v>58027</v>
+        <v>58031</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3050,7 +3050,7 @@
         <v>126840775</v>
       </c>
       <c r="B25" t="n">
-        <v>78681</v>
+        <v>78685</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>126836283</v>
       </c>
       <c r="B26" t="n">
-        <v>80145</v>
+        <v>80149</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
         <v>126836223</v>
       </c>
       <c r="B27" t="n">
-        <v>91291</v>
+        <v>91295</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3364,27 +3364,27 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126836456</v>
+        <v>126826864</v>
       </c>
       <c r="B28" t="n">
-        <v>79014</v>
+        <v>80156</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3395,14 +3395,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Slagörkullen, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>680813</v>
+        <v>680792</v>
       </c>
       <c r="R28" t="n">
-        <v>7087134</v>
+        <v>7087098</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3432,9 +3432,19 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3449,12 +3459,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3465,27 +3475,27 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126826864</v>
+        <v>126836456</v>
       </c>
       <c r="B29" t="n">
-        <v>80152</v>
+        <v>79018</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3496,14 +3506,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Slagörkullen, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>680792</v>
+        <v>680813</v>
       </c>
       <c r="R29" t="n">
-        <v>7087098</v>
+        <v>7087134</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3533,19 +3543,9 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>11:15</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>11:15</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3560,12 +3560,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3576,10 +3576,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126839926</v>
+        <v>126836448</v>
       </c>
       <c r="B30" t="n">
-        <v>75138</v>
+        <v>79018</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3587,21 +3587,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3611,10 +3611,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>680847</v>
+        <v>680910</v>
       </c>
       <c r="R30" t="n">
-        <v>7087085</v>
+        <v>7087135</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3661,12 +3661,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3677,10 +3677,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126836448</v>
+        <v>126839926</v>
       </c>
       <c r="B31" t="n">
-        <v>79014</v>
+        <v>75142</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3688,21 +3688,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3712,10 +3712,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>680910</v>
+        <v>680847</v>
       </c>
       <c r="R31" t="n">
-        <v>7087135</v>
+        <v>7087085</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3762,12 +3762,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3778,10 +3778,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126836239</v>
+        <v>126836277</v>
       </c>
       <c r="B32" t="n">
-        <v>80146</v>
+        <v>97325</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3789,21 +3789,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6462</v>
+        <v>221945</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3813,10 +3813,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>680791</v>
+        <v>680850</v>
       </c>
       <c r="R32" t="n">
-        <v>7087100</v>
+        <v>7087177</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3882,7 +3882,7 @@
         <v>126836457</v>
       </c>
       <c r="B33" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3980,10 +3980,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126836277</v>
+        <v>126836239</v>
       </c>
       <c r="B34" t="n">
-        <v>97321</v>
+        <v>80150</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3991,21 +3991,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221945</v>
+        <v>6462</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4015,10 +4015,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>680850</v>
+        <v>680791</v>
       </c>
       <c r="R34" t="n">
-        <v>7087177</v>
+        <v>7087100</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4084,7 +4084,7 @@
         <v>126838786</v>
       </c>
       <c r="B35" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         <v>126836281</v>
       </c>
       <c r="B36" t="n">
-        <v>80145</v>
+        <v>80149</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4287,7 +4287,7 @@
         <v>126839965</v>
       </c>
       <c r="B37" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4388,7 +4388,7 @@
         <v>126836358</v>
       </c>
       <c r="B38" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4489,7 +4489,7 @@
         <v>126836247</v>
       </c>
       <c r="B39" t="n">
-        <v>80021</v>
+        <v>80025</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4595,7 +4595,7 @@
         <v>126836263</v>
       </c>
       <c r="B40" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
         <v>126836359</v>
       </c>
       <c r="B41" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4807,7 +4807,7 @@
         <v>126836450</v>
       </c>
       <c r="B42" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4908,7 +4908,7 @@
         <v>126839966</v>
       </c>
       <c r="B43" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         <v>126836266</v>
       </c>
       <c r="B44" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5120,7 +5120,7 @@
         <v>126836265</v>
       </c>
       <c r="B45" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
         <v>126836540</v>
       </c>
       <c r="B46" t="n">
-        <v>78681</v>
+        <v>78685</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5329,10 +5329,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126836212</v>
+        <v>126836453</v>
       </c>
       <c r="B47" t="n">
-        <v>75138</v>
+        <v>79018</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5340,21 +5340,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5364,10 +5364,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>680844</v>
+        <v>680855</v>
       </c>
       <c r="R47" t="n">
-        <v>7087067</v>
+        <v>7087023</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5430,10 +5430,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126836453</v>
+        <v>126836212</v>
       </c>
       <c r="B48" t="n">
-        <v>79014</v>
+        <v>75142</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5441,21 +5441,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5465,10 +5465,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>680855</v>
+        <v>680844</v>
       </c>
       <c r="R48" t="n">
-        <v>7087023</v>
+        <v>7087067</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5534,7 +5534,7 @@
         <v>126836267</v>
       </c>
       <c r="B49" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5645,7 +5645,7 @@
         <v>126836213</v>
       </c>
       <c r="B50" t="n">
-        <v>75138</v>
+        <v>75142</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5746,7 +5746,7 @@
         <v>126837045</v>
       </c>
       <c r="B51" t="n">
-        <v>91326</v>
+        <v>91330</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5847,7 +5847,7 @@
         <v>126839954</v>
       </c>
       <c r="B52" t="n">
-        <v>57817</v>
+        <v>57821</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5948,7 +5948,7 @@
         <v>126836276</v>
       </c>
       <c r="B53" t="n">
-        <v>97321</v>
+        <v>97325</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6049,7 +6049,7 @@
         <v>126838799</v>
       </c>
       <c r="B54" t="n">
-        <v>98464</v>
+        <v>98468</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 64501-2023 artfynd.xlsx
+++ b/artfynd/A 64501-2023 artfynd.xlsx
@@ -776,32 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126836238</v>
+        <v>126836222</v>
       </c>
       <c r="B3" t="n">
-        <v>57821</v>
+        <v>91295</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>680851</v>
+        <v>680864</v>
       </c>
       <c r="R3" t="n">
-        <v>7087009</v>
+        <v>7087088</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,32 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126836222</v>
+        <v>126836238</v>
       </c>
       <c r="B4" t="n">
-        <v>91295</v>
+        <v>57821</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>680864</v>
+        <v>680851</v>
       </c>
       <c r="R4" t="n">
-        <v>7087088</v>
+        <v>7087009</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,32 +978,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126836455</v>
+        <v>126836243</v>
       </c>
       <c r="B5" t="n">
-        <v>79018</v>
+        <v>98468</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>680796</v>
+        <v>680867</v>
       </c>
       <c r="R5" t="n">
-        <v>7087097</v>
+        <v>7087092</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,10 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126839930</v>
+        <v>126836264</v>
       </c>
       <c r="B6" t="n">
-        <v>75142</v>
+        <v>57661</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,34 +1090,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>680800</v>
+        <v>680811</v>
       </c>
       <c r="R6" t="n">
-        <v>7087070</v>
+        <v>7087049</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1152,6 +1157,11 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>äldre ringhack (gran)</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1164,12 +1174,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1285,10 +1295,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126836264</v>
+        <v>126839930</v>
       </c>
       <c r="B8" t="n">
-        <v>57661</v>
+        <v>75142</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1296,39 +1306,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>680811</v>
+        <v>680800</v>
       </c>
       <c r="R8" t="n">
-        <v>7087049</v>
+        <v>7087070</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1363,11 +1368,6 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>äldre ringhack (gran)</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1380,12 +1380,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1396,32 +1396,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126836243</v>
+        <v>126836455</v>
       </c>
       <c r="B9" t="n">
-        <v>98468</v>
+        <v>79018</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>680867</v>
+        <v>680796</v>
       </c>
       <c r="R9" t="n">
-        <v>7087092</v>
+        <v>7087097</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1598,7 +1598,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126839943</v>
+        <v>126836499</v>
       </c>
       <c r="B11" t="n">
         <v>57661</v>
@@ -1629,7 +1629,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1638,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>680794</v>
+        <v>680839</v>
       </c>
       <c r="R11" t="n">
-        <v>7087085</v>
+        <v>7087048</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1688,12 +1688,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1704,7 +1704,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126836499</v>
+        <v>126836500</v>
       </c>
       <c r="B12" t="n">
         <v>57661</v>
@@ -1744,10 +1744,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>680839</v>
+        <v>680809</v>
       </c>
       <c r="R12" t="n">
-        <v>7087048</v>
+        <v>7087115</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1810,7 +1810,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126836500</v>
+        <v>126839943</v>
       </c>
       <c r="B13" t="n">
         <v>57661</v>
@@ -1841,7 +1841,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1850,10 +1850,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>680809</v>
+        <v>680794</v>
       </c>
       <c r="R13" t="n">
-        <v>7087115</v>
+        <v>7087085</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1900,12 +1900,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2845,45 +2845,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126836454</v>
+        <v>126838808</v>
       </c>
       <c r="B23" t="n">
-        <v>79018</v>
+        <v>58031</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Röjdtjärnviden, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>680813</v>
+        <v>680797</v>
       </c>
       <c r="R23" t="n">
-        <v>7087014</v>
+        <v>7087093</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2930,12 +2930,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -2946,45 +2946,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126838808</v>
+        <v>126836454</v>
       </c>
       <c r="B24" t="n">
-        <v>58031</v>
+        <v>79018</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Röjdtjärnviden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>680797</v>
+        <v>680813</v>
       </c>
       <c r="R24" t="n">
-        <v>7087093</v>
+        <v>7087014</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3031,12 +3031,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3263,32 +3263,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126836223</v>
+        <v>126836456</v>
       </c>
       <c r="B27" t="n">
-        <v>91295</v>
+        <v>79018</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3298,10 +3298,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>680802</v>
+        <v>680813</v>
       </c>
       <c r="R27" t="n">
-        <v>7087182</v>
+        <v>7087134</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3364,10 +3364,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126826864</v>
+        <v>126836223</v>
       </c>
       <c r="B28" t="n">
-        <v>80156</v>
+        <v>91295</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3375,34 +3375,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6463</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Slagörkullen, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>680792</v>
+        <v>680802</v>
       </c>
       <c r="R28" t="n">
-        <v>7087098</v>
+        <v>7087182</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3432,19 +3432,9 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>11:15</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>11:15</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3459,12 +3449,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3475,27 +3465,27 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126836456</v>
+        <v>126826864</v>
       </c>
       <c r="B29" t="n">
-        <v>79018</v>
+        <v>80156</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3506,14 +3496,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Slagörkullen, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>680813</v>
+        <v>680792</v>
       </c>
       <c r="R29" t="n">
-        <v>7087134</v>
+        <v>7087098</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3543,9 +3533,19 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3560,12 +3560,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3576,10 +3576,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126836448</v>
+        <v>126839926</v>
       </c>
       <c r="B30" t="n">
-        <v>79018</v>
+        <v>75142</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3587,21 +3587,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3611,10 +3611,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>680910</v>
+        <v>680847</v>
       </c>
       <c r="R30" t="n">
-        <v>7087135</v>
+        <v>7087085</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3661,12 +3661,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3677,10 +3677,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126839926</v>
+        <v>126836448</v>
       </c>
       <c r="B31" t="n">
-        <v>75142</v>
+        <v>79018</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3688,21 +3688,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3712,10 +3712,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>680847</v>
+        <v>680910</v>
       </c>
       <c r="R31" t="n">
-        <v>7087085</v>
+        <v>7087135</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3762,12 +3762,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3778,32 +3778,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126836277</v>
+        <v>126836457</v>
       </c>
       <c r="B32" t="n">
-        <v>97325</v>
+        <v>79018</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3813,10 +3813,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>680850</v>
+        <v>680830</v>
       </c>
       <c r="R32" t="n">
-        <v>7087177</v>
+        <v>7087203</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3879,32 +3879,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126836457</v>
+        <v>126836239</v>
       </c>
       <c r="B33" t="n">
-        <v>79018</v>
+        <v>80150</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3914,10 +3914,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>680830</v>
+        <v>680791</v>
       </c>
       <c r="R33" t="n">
-        <v>7087203</v>
+        <v>7087100</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3980,10 +3980,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126836239</v>
+        <v>126836277</v>
       </c>
       <c r="B34" t="n">
-        <v>80150</v>
+        <v>97325</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3991,21 +3991,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6462</v>
+        <v>221945</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4015,10 +4015,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>680791</v>
+        <v>680850</v>
       </c>
       <c r="R34" t="n">
-        <v>7087100</v>
+        <v>7087177</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4905,10 +4905,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126839966</v>
+        <v>126836265</v>
       </c>
       <c r="B43" t="n">
-        <v>79636</v>
+        <v>57661</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4916,34 +4916,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>680908</v>
+        <v>680876</v>
       </c>
       <c r="R43" t="n">
-        <v>7087111</v>
+        <v>7086899</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4978,6 +4983,11 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>färska ringhack (gran)</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -4990,12 +5000,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5006,10 +5016,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126836266</v>
+        <v>126839966</v>
       </c>
       <c r="B44" t="n">
-        <v>57661</v>
+        <v>79636</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5017,39 +5027,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>680870</v>
+        <v>680908</v>
       </c>
       <c r="R44" t="n">
-        <v>7086922</v>
+        <v>7087111</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5084,11 +5089,6 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Färska ringhack på nyligen tillskapad högstubbe i samband med av SCA genomförd illegal avverkning</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5101,12 +5101,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5117,7 +5117,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126836265</v>
+        <v>126836266</v>
       </c>
       <c r="B45" t="n">
         <v>57661</v>
@@ -5157,10 +5157,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>680876</v>
+        <v>680870</v>
       </c>
       <c r="R45" t="n">
-        <v>7086899</v>
+        <v>7086922</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5197,7 +5197,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>färska ringhack (gran)</t>
+          <t>Färska ringhack på nyligen tillskapad högstubbe i samband med av SCA genomförd illegal avverkning</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5329,10 +5329,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126836453</v>
+        <v>126836267</v>
       </c>
       <c r="B47" t="n">
-        <v>79018</v>
+        <v>57661</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5340,34 +5340,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>680855</v>
+        <v>680851</v>
       </c>
       <c r="R47" t="n">
-        <v>7087023</v>
+        <v>7087171</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5400,6 +5405,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5531,10 +5541,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126836267</v>
+        <v>126836453</v>
       </c>
       <c r="B49" t="n">
-        <v>57661</v>
+        <v>79018</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5542,39 +5552,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>680851</v>
+        <v>680855</v>
       </c>
       <c r="R49" t="n">
-        <v>7087171</v>
+        <v>7087023</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5607,11 +5612,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5743,10 +5743,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126837045</v>
+        <v>126839954</v>
       </c>
       <c r="B51" t="n">
-        <v>91330</v>
+        <v>57821</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5754,34 +5754,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>680812</v>
+        <v>680871</v>
       </c>
       <c r="R51" t="n">
-        <v>7086987</v>
+        <v>7087130</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5828,12 +5828,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -5844,10 +5844,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126839954</v>
+        <v>126837045</v>
       </c>
       <c r="B52" t="n">
-        <v>57821</v>
+        <v>91330</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5855,34 +5855,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>680871</v>
+        <v>680812</v>
       </c>
       <c r="R52" t="n">
-        <v>7087130</v>
+        <v>7086987</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5929,12 +5929,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">

--- a/artfynd/A 64501-2023 artfynd.xlsx
+++ b/artfynd/A 64501-2023 artfynd.xlsx
@@ -2744,32 +2744,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126839980</v>
+        <v>126836454</v>
       </c>
       <c r="B22" t="n">
-        <v>75127</v>
+        <v>79018</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>306</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>680796</v>
+        <v>680813</v>
       </c>
       <c r="R22" t="n">
-        <v>7087081</v>
+        <v>7087014</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2829,12 +2829,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2845,10 +2845,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126838808</v>
+        <v>126839980</v>
       </c>
       <c r="B23" t="n">
-        <v>58031</v>
+        <v>75127</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2856,34 +2856,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103015</v>
+        <v>306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Röjdtjärnviden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>680797</v>
+        <v>680796</v>
       </c>
       <c r="R23" t="n">
-        <v>7087093</v>
+        <v>7087081</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2930,12 +2930,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -2946,45 +2946,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126836454</v>
+        <v>126838808</v>
       </c>
       <c r="B24" t="n">
-        <v>79018</v>
+        <v>58031</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Röjdtjärnviden, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>680813</v>
+        <v>680797</v>
       </c>
       <c r="R24" t="n">
-        <v>7087014</v>
+        <v>7087093</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3031,12 +3031,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -4905,10 +4905,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126836265</v>
+        <v>126839966</v>
       </c>
       <c r="B43" t="n">
-        <v>57661</v>
+        <v>79636</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4916,39 +4916,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>680876</v>
+        <v>680908</v>
       </c>
       <c r="R43" t="n">
-        <v>7086899</v>
+        <v>7087111</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4983,11 +4978,6 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>färska ringhack (gran)</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5000,12 +4990,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5016,10 +5006,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126839966</v>
+        <v>126836265</v>
       </c>
       <c r="B44" t="n">
-        <v>79636</v>
+        <v>57661</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5027,34 +5017,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>680908</v>
+        <v>680876</v>
       </c>
       <c r="R44" t="n">
-        <v>7087111</v>
+        <v>7086899</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5089,6 +5084,11 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>färska ringhack (gran)</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5101,12 +5101,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">

--- a/artfynd/A 64501-2023 artfynd.xlsx
+++ b/artfynd/A 64501-2023 artfynd.xlsx
@@ -2542,10 +2542,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126836282</v>
+        <v>126840006</v>
       </c>
       <c r="B20" t="n">
-        <v>80149</v>
+        <v>8439</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2553,21 +2553,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6461</v>
+        <v>106554</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2577,10 +2577,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>680867</v>
+        <v>680902</v>
       </c>
       <c r="R20" t="n">
-        <v>7087092</v>
+        <v>7087115</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2627,12 +2627,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2643,10 +2643,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126840006</v>
+        <v>126836282</v>
       </c>
       <c r="B21" t="n">
-        <v>8439</v>
+        <v>80149</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2654,21 +2654,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106554</v>
+        <v>6461</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2678,10 +2678,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>680902</v>
+        <v>680867</v>
       </c>
       <c r="R21" t="n">
-        <v>7087115</v>
+        <v>7087092</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2728,12 +2728,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -3263,32 +3263,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126836456</v>
+        <v>126836223</v>
       </c>
       <c r="B27" t="n">
-        <v>79018</v>
+        <v>91295</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3298,10 +3298,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>680813</v>
+        <v>680802</v>
       </c>
       <c r="R27" t="n">
-        <v>7087134</v>
+        <v>7087182</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3364,32 +3364,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126836223</v>
+        <v>126836456</v>
       </c>
       <c r="B28" t="n">
-        <v>91295</v>
+        <v>79018</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3399,10 +3399,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>680802</v>
+        <v>680813</v>
       </c>
       <c r="R28" t="n">
-        <v>7087182</v>
+        <v>7087134</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 64501-2023 artfynd.xlsx
+++ b/artfynd/A 64501-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126839924</v>
+        <v>126836238</v>
       </c>
       <c r="B2" t="n">
-        <v>75142</v>
+        <v>57821</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>680859</v>
+        <v>680851</v>
       </c>
       <c r="R2" t="n">
-        <v>7087090</v>
+        <v>7087009</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,12 +760,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126836238</v>
+        <v>126839924</v>
       </c>
       <c r="B4" t="n">
-        <v>57821</v>
+        <v>75142</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>6440</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>680851</v>
+        <v>680859</v>
       </c>
       <c r="R4" t="n">
-        <v>7087009</v>
+        <v>7087090</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -962,12 +962,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -978,32 +978,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126836243</v>
+        <v>126839930</v>
       </c>
       <c r="B5" t="n">
-        <v>98468</v>
+        <v>75142</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221952</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>680867</v>
+        <v>680800</v>
       </c>
       <c r="R5" t="n">
-        <v>7087092</v>
+        <v>7087070</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,12 +1063,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1079,10 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126836264</v>
+        <v>126836455</v>
       </c>
       <c r="B6" t="n">
-        <v>57661</v>
+        <v>79018</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,39 +1090,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>680811</v>
+        <v>680796</v>
       </c>
       <c r="R6" t="n">
-        <v>7087049</v>
+        <v>7087097</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1155,11 +1150,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1190,7 +1180,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126836229</v>
+        <v>126836264</v>
       </c>
       <c r="B7" t="n">
         <v>57661</v>
@@ -1218,9 +1208,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1229,10 +1220,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>680850</v>
+        <v>680811</v>
       </c>
       <c r="R7" t="n">
-        <v>7087177</v>
+        <v>7087049</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1265,6 +1256,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1295,10 +1291,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126839930</v>
+        <v>126836229</v>
       </c>
       <c r="B8" t="n">
-        <v>75142</v>
+        <v>57661</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1306,34 +1302,38 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>680800</v>
+        <v>680850</v>
       </c>
       <c r="R8" t="n">
-        <v>7087070</v>
+        <v>7087177</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1380,12 +1380,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1396,32 +1396,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126836455</v>
+        <v>126836243</v>
       </c>
       <c r="B9" t="n">
-        <v>79018</v>
+        <v>98469</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>680796</v>
+        <v>680867</v>
       </c>
       <c r="R9" t="n">
-        <v>7087097</v>
+        <v>7087092</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1598,7 +1598,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126836499</v>
+        <v>126839943</v>
       </c>
       <c r="B11" t="n">
         <v>57661</v>
@@ -1629,7 +1629,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1638,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>680839</v>
+        <v>680794</v>
       </c>
       <c r="R11" t="n">
-        <v>7087048</v>
+        <v>7087085</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1688,12 +1688,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1704,7 +1704,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126836500</v>
+        <v>126836499</v>
       </c>
       <c r="B12" t="n">
         <v>57661</v>
@@ -1744,10 +1744,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>680809</v>
+        <v>680839</v>
       </c>
       <c r="R12" t="n">
-        <v>7087115</v>
+        <v>7087048</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1810,7 +1810,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126839943</v>
+        <v>126836500</v>
       </c>
       <c r="B13" t="n">
         <v>57661</v>
@@ -1841,7 +1841,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1850,10 +1850,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>680794</v>
+        <v>680809</v>
       </c>
       <c r="R13" t="n">
-        <v>7087085</v>
+        <v>7087115</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1900,12 +1900,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1916,45 +1916,50 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126839925</v>
+        <v>126836258</v>
       </c>
       <c r="B14" t="n">
-        <v>75127</v>
+        <v>57661</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>306</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>680859</v>
+        <v>680805</v>
       </c>
       <c r="R14" t="n">
-        <v>7087090</v>
+        <v>7087122</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1989,6 +1994,11 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran) intill djupa körspår efter illegal avverkning genomförd av SCA</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2001,12 +2011,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2017,32 +2027,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126836451</v>
+        <v>126839925</v>
       </c>
       <c r="B15" t="n">
-        <v>79018</v>
+        <v>75127</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2052,10 +2062,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>680864</v>
+        <v>680859</v>
       </c>
       <c r="R15" t="n">
-        <v>7087091</v>
+        <v>7087090</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2102,12 +2112,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2118,10 +2128,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126836465</v>
+        <v>126836260</v>
       </c>
       <c r="B16" t="n">
-        <v>79018</v>
+        <v>57661</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2129,34 +2139,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>680782</v>
+        <v>680809</v>
       </c>
       <c r="R16" t="n">
-        <v>7087268</v>
+        <v>7087061</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2189,6 +2204,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran) intill djupa körspår efter illegal avverkning genomförd av SCA</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2219,10 +2239,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126836260</v>
+        <v>126836451</v>
       </c>
       <c r="B17" t="n">
-        <v>57661</v>
+        <v>79018</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2230,39 +2250,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>680809</v>
+        <v>680864</v>
       </c>
       <c r="R17" t="n">
-        <v>7087061</v>
+        <v>7087091</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2295,11 +2310,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran) intill djupa körspår efter illegal avverkning genomförd av SCA</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2330,10 +2340,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126836258</v>
+        <v>126836465</v>
       </c>
       <c r="B18" t="n">
-        <v>57661</v>
+        <v>79018</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2341,39 +2351,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>680805</v>
+        <v>680782</v>
       </c>
       <c r="R18" t="n">
-        <v>7087122</v>
+        <v>7087268</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2406,11 +2411,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran) intill djupa körspår efter illegal avverkning genomförd av SCA</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2441,32 +2441,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126836452</v>
+        <v>126840006</v>
       </c>
       <c r="B19" t="n">
-        <v>79018</v>
+        <v>8439</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>106554</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2476,10 +2476,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>680856</v>
+        <v>680902</v>
       </c>
       <c r="R19" t="n">
-        <v>7087078</v>
+        <v>7087115</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2526,12 +2526,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2542,32 +2542,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126840006</v>
+        <v>126836452</v>
       </c>
       <c r="B20" t="n">
-        <v>8439</v>
+        <v>79018</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106554</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2577,10 +2577,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>680902</v>
+        <v>680856</v>
       </c>
       <c r="R20" t="n">
-        <v>7087115</v>
+        <v>7087078</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2627,12 +2627,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2845,10 +2845,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126839980</v>
+        <v>126838808</v>
       </c>
       <c r="B23" t="n">
-        <v>75127</v>
+        <v>58031</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2856,34 +2856,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>306</v>
+        <v>103015</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Röjdtjärnviden, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>680796</v>
+        <v>680797</v>
       </c>
       <c r="R23" t="n">
-        <v>7087081</v>
+        <v>7087093</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2930,12 +2930,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -2946,10 +2946,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126838808</v>
+        <v>126839980</v>
       </c>
       <c r="B24" t="n">
-        <v>58031</v>
+        <v>75127</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2957,34 +2957,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103015</v>
+        <v>306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Röjdtjärnviden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>680797</v>
+        <v>680796</v>
       </c>
       <c r="R24" t="n">
-        <v>7087093</v>
+        <v>7087081</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3031,12 +3031,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3263,32 +3263,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126836223</v>
+        <v>126836456</v>
       </c>
       <c r="B27" t="n">
-        <v>91295</v>
+        <v>79018</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3298,10 +3298,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>680802</v>
+        <v>680813</v>
       </c>
       <c r="R27" t="n">
-        <v>7087182</v>
+        <v>7087134</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3364,32 +3364,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126836456</v>
+        <v>126836223</v>
       </c>
       <c r="B28" t="n">
-        <v>79018</v>
+        <v>91295</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3399,10 +3399,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>680813</v>
+        <v>680802</v>
       </c>
       <c r="R28" t="n">
-        <v>7087134</v>
+        <v>7087182</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3576,10 +3576,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126839926</v>
+        <v>126836448</v>
       </c>
       <c r="B30" t="n">
-        <v>75142</v>
+        <v>79018</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3587,21 +3587,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3611,10 +3611,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>680847</v>
+        <v>680910</v>
       </c>
       <c r="R30" t="n">
-        <v>7087085</v>
+        <v>7087135</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3661,12 +3661,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3677,10 +3677,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126836448</v>
+        <v>126839926</v>
       </c>
       <c r="B31" t="n">
-        <v>79018</v>
+        <v>75142</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3688,21 +3688,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3712,10 +3712,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>680910</v>
+        <v>680847</v>
       </c>
       <c r="R31" t="n">
-        <v>7087135</v>
+        <v>7087085</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3762,12 +3762,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3778,32 +3778,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126836457</v>
+        <v>126836239</v>
       </c>
       <c r="B32" t="n">
-        <v>79018</v>
+        <v>80150</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3813,10 +3813,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>680830</v>
+        <v>680791</v>
       </c>
       <c r="R32" t="n">
-        <v>7087203</v>
+        <v>7087100</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3879,32 +3879,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126836239</v>
+        <v>126836457</v>
       </c>
       <c r="B33" t="n">
-        <v>80150</v>
+        <v>79018</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3914,10 +3914,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>680791</v>
+        <v>680830</v>
       </c>
       <c r="R33" t="n">
-        <v>7087100</v>
+        <v>7087203</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4385,32 +4385,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126836358</v>
+        <v>126836247</v>
       </c>
       <c r="B38" t="n">
-        <v>79018</v>
+        <v>80025</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4420,10 +4420,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>680811</v>
+        <v>680772</v>
       </c>
       <c r="R38" t="n">
-        <v>7086966</v>
+        <v>7087294</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4456,6 +4456,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>På asplåga</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4486,32 +4491,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126836247</v>
+        <v>126836358</v>
       </c>
       <c r="B39" t="n">
-        <v>80025</v>
+        <v>79018</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4521,10 +4526,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>680772</v>
+        <v>680811</v>
       </c>
       <c r="R39" t="n">
-        <v>7087294</v>
+        <v>7086966</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4557,11 +4562,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>På asplåga</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5006,7 +5006,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126836265</v>
+        <v>126836266</v>
       </c>
       <c r="B44" t="n">
         <v>57661</v>
@@ -5046,10 +5046,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>680876</v>
+        <v>680870</v>
       </c>
       <c r="R44" t="n">
-        <v>7086899</v>
+        <v>7086922</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>färska ringhack (gran)</t>
+          <t>Färska ringhack på nyligen tillskapad högstubbe i samband med av SCA genomförd illegal avverkning</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5117,7 +5117,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126836266</v>
+        <v>126836265</v>
       </c>
       <c r="B45" t="n">
         <v>57661</v>
@@ -5157,10 +5157,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>680870</v>
+        <v>680876</v>
       </c>
       <c r="R45" t="n">
-        <v>7086922</v>
+        <v>7086899</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5197,7 +5197,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Färska ringhack på nyligen tillskapad högstubbe i samband med av SCA genomförd illegal avverkning</t>
+          <t>färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5329,10 +5329,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126836267</v>
+        <v>126836453</v>
       </c>
       <c r="B47" t="n">
-        <v>57661</v>
+        <v>79018</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5340,39 +5340,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>680851</v>
+        <v>680855</v>
       </c>
       <c r="R47" t="n">
-        <v>7087171</v>
+        <v>7087023</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5405,11 +5400,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5541,10 +5531,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126836453</v>
+        <v>126836267</v>
       </c>
       <c r="B49" t="n">
-        <v>79018</v>
+        <v>57661</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5552,34 +5542,39 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>680855</v>
+        <v>680851</v>
       </c>
       <c r="R49" t="n">
-        <v>7087023</v>
+        <v>7087171</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5612,6 +5607,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5642,10 +5642,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126836213</v>
+        <v>126837045</v>
       </c>
       <c r="B50" t="n">
-        <v>75142</v>
+        <v>91330</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5653,34 +5653,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>680800</v>
+        <v>680812</v>
       </c>
       <c r="R50" t="n">
-        <v>7087109</v>
+        <v>7086987</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5727,12 +5727,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -5743,10 +5743,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126839954</v>
+        <v>126836213</v>
       </c>
       <c r="B51" t="n">
-        <v>57821</v>
+        <v>75142</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5754,21 +5754,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103021</v>
+        <v>6440</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5778,10 +5778,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>680871</v>
+        <v>680800</v>
       </c>
       <c r="R51" t="n">
-        <v>7087130</v>
+        <v>7087109</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5828,12 +5828,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -5844,10 +5844,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126837045</v>
+        <v>126839954</v>
       </c>
       <c r="B52" t="n">
-        <v>91330</v>
+        <v>57821</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5855,34 +5855,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>680812</v>
+        <v>680871</v>
       </c>
       <c r="R52" t="n">
-        <v>7086987</v>
+        <v>7087130</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5929,12 +5929,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -5945,10 +5945,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126836276</v>
+        <v>126838799</v>
       </c>
       <c r="B53" t="n">
-        <v>97325</v>
+        <v>98469</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5956,34 +5956,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221945</v>
+        <v>221952</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Röjdtjärnviden, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>680857</v>
+        <v>680795</v>
       </c>
       <c r="R53" t="n">
-        <v>7087050</v>
+        <v>7087239</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6030,26 +6030,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY53" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126838799</v>
+        <v>126836276</v>
       </c>
       <c r="B54" t="n">
-        <v>98468</v>
+        <v>97325</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6057,34 +6053,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Röjdtjärnviden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>680795</v>
+        <v>680857</v>
       </c>
       <c r="R54" t="n">
-        <v>7087239</v>
+        <v>7087050</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6131,15 +6127,19 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY54" t="inlineStr"/>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 64501-2023 artfynd.xlsx
+++ b/artfynd/A 64501-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY54"/>
+  <dimension ref="A1:AY55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6141,6 +6141,103 @@
         </is>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>129165771</v>
+      </c>
+      <c r="B55" t="n">
+        <v>97527</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Bredträsk, Ång</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>680910</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7086910</v>
+      </c>
+      <c r="S55" t="n">
+        <v>5</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2021-10-05</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2021-10-15</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Isak Sarac</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Via Isak Sarac</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 64501-2023 artfynd.xlsx
+++ b/artfynd/A 64501-2023 artfynd.xlsx
@@ -6146,7 +6146,7 @@
         <v>129165771</v>
       </c>
       <c r="B55" t="n">
-        <v>97527</v>
+        <v>97530</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 64501-2023 artfynd.xlsx
+++ b/artfynd/A 64501-2023 artfynd.xlsx
@@ -6146,7 +6146,7 @@
         <v>129165771</v>
       </c>
       <c r="B55" t="n">
-        <v>97530</v>
+        <v>97540</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 64501-2023 artfynd.xlsx
+++ b/artfynd/A 64501-2023 artfynd.xlsx
@@ -6146,7 +6146,7 @@
         <v>129165771</v>
       </c>
       <c r="B55" t="n">
-        <v>97540</v>
+        <v>97547</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 64501-2023 artfynd.xlsx
+++ b/artfynd/A 64501-2023 artfynd.xlsx
@@ -6146,7 +6146,7 @@
         <v>129165771</v>
       </c>
       <c r="B55" t="n">
-        <v>97547</v>
+        <v>97549</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 64501-2023 artfynd.xlsx
+++ b/artfynd/A 64501-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY55"/>
+  <dimension ref="A1:AY54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6141,103 +6141,6 @@
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" t="n">
-        <v>129165771</v>
-      </c>
-      <c r="B55" t="n">
-        <v>97549</v>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E55" t="n">
-        <v>221945</v>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="P55" t="inlineStr">
-        <is>
-          <t>Bredträsk, Ång</t>
-        </is>
-      </c>
-      <c r="Q55" t="n">
-        <v>680910</v>
-      </c>
-      <c r="R55" t="n">
-        <v>7086910</v>
-      </c>
-      <c r="S55" t="n">
-        <v>5</v>
-      </c>
-      <c r="T55" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U55" t="inlineStr">
-        <is>
-          <t>Bjurholm</t>
-        </is>
-      </c>
-      <c r="V55" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W55" t="inlineStr">
-        <is>
-          <t>Bjurholm</t>
-        </is>
-      </c>
-      <c r="Y55" t="inlineStr">
-        <is>
-          <t>2021-10-05</t>
-        </is>
-      </c>
-      <c r="AA55" t="inlineStr">
-        <is>
-          <t>2021-10-15</t>
-        </is>
-      </c>
-      <c r="AD55" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE55" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG55" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT55" t="inlineStr"/>
-      <c r="AW55" t="inlineStr">
-        <is>
-          <t>Isak Sarac</t>
-        </is>
-      </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>Via Isak Sarac</t>
-        </is>
-      </c>
-      <c r="AY55" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 64501-2023 artfynd.xlsx
+++ b/artfynd/A 64501-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126836238</v>
       </c>
       <c r="B2" t="n">
-        <v>57821</v>
+        <v>57817</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>126836222</v>
       </c>
       <c r="B3" t="n">
-        <v>91295</v>
+        <v>91284</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>126839924</v>
       </c>
       <c r="B4" t="n">
-        <v>75142</v>
+        <v>75135</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,10 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126839930</v>
+        <v>126836264</v>
       </c>
       <c r="B5" t="n">
-        <v>75142</v>
+        <v>57657</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -989,34 +989,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>680800</v>
+        <v>680811</v>
       </c>
       <c r="R5" t="n">
-        <v>7087070</v>
+        <v>7087049</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1051,6 +1056,11 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>äldre ringhack (gran)</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1063,12 +1073,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1079,10 +1089,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126836455</v>
+        <v>126836229</v>
       </c>
       <c r="B6" t="n">
-        <v>79018</v>
+        <v>57657</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,34 +1100,38 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>680796</v>
+        <v>680850</v>
       </c>
       <c r="R6" t="n">
-        <v>7087097</v>
+        <v>7087177</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1180,10 +1194,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126836264</v>
+        <v>126839930</v>
       </c>
       <c r="B7" t="n">
-        <v>57661</v>
+        <v>75135</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,39 +1205,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>680811</v>
+        <v>680800</v>
       </c>
       <c r="R7" t="n">
-        <v>7087049</v>
+        <v>7087070</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1258,11 +1267,6 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>äldre ringhack (gran)</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1275,12 +1279,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1291,10 +1295,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126836229</v>
+        <v>126836455</v>
       </c>
       <c r="B8" t="n">
-        <v>57661</v>
+        <v>79011</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1302,38 +1306,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>680850</v>
+        <v>680796</v>
       </c>
       <c r="R8" t="n">
-        <v>7087177</v>
+        <v>7087097</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1399,7 +1399,7 @@
         <v>126836243</v>
       </c>
       <c r="B9" t="n">
-        <v>98469</v>
+        <v>98457</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>126836248</v>
       </c>
       <c r="B10" t="n">
-        <v>80025</v>
+        <v>80018</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>126839943</v>
       </c>
       <c r="B11" t="n">
-        <v>57661</v>
+        <v>57657</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>126836499</v>
       </c>
       <c r="B12" t="n">
-        <v>57661</v>
+        <v>57657</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>126836500</v>
       </c>
       <c r="B13" t="n">
-        <v>57661</v>
+        <v>57657</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1916,50 +1916,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126836258</v>
+        <v>126839925</v>
       </c>
       <c r="B14" t="n">
-        <v>57661</v>
+        <v>75120</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>680805</v>
+        <v>680859</v>
       </c>
       <c r="R14" t="n">
-        <v>7087122</v>
+        <v>7087090</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1994,11 +1989,6 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran) intill djupa körspår efter illegal avverkning genomförd av SCA</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2011,12 +2001,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2027,45 +2017,50 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126839925</v>
+        <v>126836260</v>
       </c>
       <c r="B15" t="n">
-        <v>75127</v>
+        <v>57657</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>306</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>680859</v>
+        <v>680809</v>
       </c>
       <c r="R15" t="n">
-        <v>7087090</v>
+        <v>7087061</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2100,6 +2095,11 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran) intill djupa körspår efter illegal avverkning genomförd av SCA</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2112,12 +2112,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2128,10 +2128,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126836260</v>
+        <v>126836258</v>
       </c>
       <c r="B16" t="n">
-        <v>57661</v>
+        <v>57657</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>680809</v>
+        <v>680805</v>
       </c>
       <c r="R16" t="n">
-        <v>7087061</v>
+        <v>7087122</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2242,7 +2242,7 @@
         <v>126836451</v>
       </c>
       <c r="B17" t="n">
-        <v>79018</v>
+        <v>79011</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
         <v>126836465</v>
       </c>
       <c r="B18" t="n">
-        <v>79018</v>
+        <v>79011</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2441,10 +2441,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126840006</v>
+        <v>126836282</v>
       </c>
       <c r="B19" t="n">
-        <v>8439</v>
+        <v>80142</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2452,21 +2452,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106554</v>
+        <v>6461</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2476,10 +2476,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>680902</v>
+        <v>680867</v>
       </c>
       <c r="R19" t="n">
-        <v>7087115</v>
+        <v>7087092</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2526,12 +2526,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2545,7 +2545,7 @@
         <v>126836452</v>
       </c>
       <c r="B20" t="n">
-        <v>79018</v>
+        <v>79011</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2643,10 +2643,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126836282</v>
+        <v>126840006</v>
       </c>
       <c r="B21" t="n">
-        <v>80149</v>
+        <v>8436</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2654,21 +2654,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6461</v>
+        <v>106554</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2678,10 +2678,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>680867</v>
+        <v>680902</v>
       </c>
       <c r="R21" t="n">
-        <v>7087092</v>
+        <v>7087115</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2728,12 +2728,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2744,32 +2744,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126836454</v>
+        <v>126839980</v>
       </c>
       <c r="B22" t="n">
-        <v>79018</v>
+        <v>75120</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>680813</v>
+        <v>680796</v>
       </c>
       <c r="R22" t="n">
-        <v>7087014</v>
+        <v>7087081</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2829,12 +2829,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2848,7 +2848,7 @@
         <v>126838808</v>
       </c>
       <c r="B23" t="n">
-        <v>58031</v>
+        <v>58027</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2946,32 +2946,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126839980</v>
+        <v>126836454</v>
       </c>
       <c r="B24" t="n">
-        <v>75127</v>
+        <v>79011</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>306</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2981,10 +2981,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>680796</v>
+        <v>680813</v>
       </c>
       <c r="R24" t="n">
-        <v>7087081</v>
+        <v>7087014</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3031,12 +3031,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3047,48 +3047,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126840775</v>
+        <v>126836283</v>
       </c>
       <c r="B25" t="n">
-        <v>78685</v>
+        <v>80142</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>353</v>
+        <v>6461</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Lämkullen, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>680905</v>
+        <v>680788</v>
       </c>
       <c r="R25" t="n">
-        <v>7087125</v>
+        <v>7087194</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3118,40 +3115,29 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>11:49</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>11:49</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3162,45 +3148,48 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126836283</v>
+        <v>126840775</v>
       </c>
       <c r="B26" t="n">
-        <v>80149</v>
+        <v>78678</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6461</v>
+        <v>353</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Lämkullen, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>680788</v>
+        <v>680905</v>
       </c>
       <c r="R26" t="n">
-        <v>7087194</v>
+        <v>7087125</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3230,29 +3219,40 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3263,27 +3263,27 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126836456</v>
+        <v>126826864</v>
       </c>
       <c r="B27" t="n">
-        <v>79018</v>
+        <v>80149</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3294,14 +3294,14 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Slagörkullen, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>680813</v>
+        <v>680792</v>
       </c>
       <c r="R27" t="n">
-        <v>7087134</v>
+        <v>7087098</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3331,9 +3331,19 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3348,12 +3358,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3364,32 +3374,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126836223</v>
+        <v>126836456</v>
       </c>
       <c r="B28" t="n">
-        <v>91295</v>
+        <v>79011</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3399,10 +3409,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>680802</v>
+        <v>680813</v>
       </c>
       <c r="R28" t="n">
-        <v>7087182</v>
+        <v>7087134</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3465,10 +3475,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126826864</v>
+        <v>126836223</v>
       </c>
       <c r="B29" t="n">
-        <v>80156</v>
+        <v>91284</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3476,34 +3486,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6463</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Slagörkullen, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>680792</v>
+        <v>680802</v>
       </c>
       <c r="R29" t="n">
-        <v>7087098</v>
+        <v>7087182</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3533,19 +3543,9 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>11:15</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>11:15</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3560,12 +3560,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3576,10 +3576,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126836448</v>
+        <v>126839926</v>
       </c>
       <c r="B30" t="n">
-        <v>79018</v>
+        <v>75135</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3587,21 +3587,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3611,10 +3611,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>680910</v>
+        <v>680847</v>
       </c>
       <c r="R30" t="n">
-        <v>7087135</v>
+        <v>7087085</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3661,12 +3661,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3677,10 +3677,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126839926</v>
+        <v>126836448</v>
       </c>
       <c r="B31" t="n">
-        <v>75142</v>
+        <v>79011</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3688,21 +3688,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3712,10 +3712,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>680847</v>
+        <v>680910</v>
       </c>
       <c r="R31" t="n">
-        <v>7087085</v>
+        <v>7087135</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3762,12 +3762,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3781,7 +3781,7 @@
         <v>126836239</v>
       </c>
       <c r="B32" t="n">
-        <v>80150</v>
+        <v>80143</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3879,32 +3879,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126836457</v>
+        <v>126836277</v>
       </c>
       <c r="B33" t="n">
-        <v>79018</v>
+        <v>97314</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3914,10 +3914,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>680830</v>
+        <v>680850</v>
       </c>
       <c r="R33" t="n">
-        <v>7087203</v>
+        <v>7087177</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3980,32 +3980,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126836277</v>
+        <v>126836457</v>
       </c>
       <c r="B34" t="n">
-        <v>97325</v>
+        <v>79011</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4015,10 +4015,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>680850</v>
+        <v>680830</v>
       </c>
       <c r="R34" t="n">
-        <v>7087177</v>
+        <v>7087203</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4084,7 +4084,7 @@
         <v>126838786</v>
       </c>
       <c r="B35" t="n">
-        <v>57661</v>
+        <v>57657</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         <v>126836281</v>
       </c>
       <c r="B36" t="n">
-        <v>80149</v>
+        <v>80142</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4287,7 +4287,7 @@
         <v>126839965</v>
       </c>
       <c r="B37" t="n">
-        <v>78777</v>
+        <v>78770</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4385,32 +4385,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126836247</v>
+        <v>126836358</v>
       </c>
       <c r="B38" t="n">
-        <v>80025</v>
+        <v>79011</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4420,10 +4420,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>680772</v>
+        <v>680811</v>
       </c>
       <c r="R38" t="n">
-        <v>7087294</v>
+        <v>7086966</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4456,11 +4456,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>På asplåga</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4491,10 +4486,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126836358</v>
+        <v>126836263</v>
       </c>
       <c r="B39" t="n">
-        <v>79018</v>
+        <v>57657</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4502,34 +4497,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>680811</v>
+        <v>680847</v>
       </c>
       <c r="R39" t="n">
-        <v>7086966</v>
+        <v>7087070</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4562,6 +4562,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4592,50 +4597,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126836263</v>
+        <v>126836247</v>
       </c>
       <c r="B40" t="n">
-        <v>57661</v>
+        <v>80018</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>680847</v>
+        <v>680772</v>
       </c>
       <c r="R40" t="n">
-        <v>7087070</v>
+        <v>7087294</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>äldre ringhack (gran)</t>
+          <t>På asplåga</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4706,7 +4706,7 @@
         <v>126836359</v>
       </c>
       <c r="B41" t="n">
-        <v>79018</v>
+        <v>79011</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4807,7 +4807,7 @@
         <v>126836450</v>
       </c>
       <c r="B42" t="n">
-        <v>79018</v>
+        <v>79011</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4905,10 +4905,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126839966</v>
+        <v>126836265</v>
       </c>
       <c r="B43" t="n">
-        <v>79636</v>
+        <v>57657</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4916,34 +4916,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>680908</v>
+        <v>680876</v>
       </c>
       <c r="R43" t="n">
-        <v>7087111</v>
+        <v>7086899</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4978,6 +4983,11 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>färska ringhack (gran)</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -4990,12 +5000,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5006,10 +5016,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126836266</v>
+        <v>126839966</v>
       </c>
       <c r="B44" t="n">
-        <v>57661</v>
+        <v>79629</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5017,39 +5027,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>680870</v>
+        <v>680908</v>
       </c>
       <c r="R44" t="n">
-        <v>7086922</v>
+        <v>7087111</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5084,11 +5089,6 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Färska ringhack på nyligen tillskapad högstubbe i samband med av SCA genomförd illegal avverkning</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5101,12 +5101,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5117,10 +5117,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126836265</v>
+        <v>126836266</v>
       </c>
       <c r="B45" t="n">
-        <v>57661</v>
+        <v>57657</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5157,10 +5157,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>680876</v>
+        <v>680870</v>
       </c>
       <c r="R45" t="n">
-        <v>7086899</v>
+        <v>7086922</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5197,7 +5197,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>färska ringhack (gran)</t>
+          <t>Färska ringhack på nyligen tillskapad högstubbe i samband med av SCA genomförd illegal avverkning</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5231,7 +5231,7 @@
         <v>126836540</v>
       </c>
       <c r="B46" t="n">
-        <v>78685</v>
+        <v>78678</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5329,10 +5329,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126836453</v>
+        <v>126836212</v>
       </c>
       <c r="B47" t="n">
-        <v>79018</v>
+        <v>75135</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5340,21 +5340,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5364,10 +5364,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>680855</v>
+        <v>680844</v>
       </c>
       <c r="R47" t="n">
-        <v>7087023</v>
+        <v>7087067</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5430,10 +5430,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126836212</v>
+        <v>126836453</v>
       </c>
       <c r="B48" t="n">
-        <v>75142</v>
+        <v>79011</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5441,21 +5441,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5465,10 +5465,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>680844</v>
+        <v>680855</v>
       </c>
       <c r="R48" t="n">
-        <v>7087067</v>
+        <v>7087023</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5534,7 +5534,7 @@
         <v>126836267</v>
       </c>
       <c r="B49" t="n">
-        <v>57661</v>
+        <v>57657</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5645,7 +5645,7 @@
         <v>126837045</v>
       </c>
       <c r="B50" t="n">
-        <v>91330</v>
+        <v>91319</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5743,10 +5743,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126836213</v>
+        <v>126839954</v>
       </c>
       <c r="B51" t="n">
-        <v>75142</v>
+        <v>57817</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5754,21 +5754,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6440</v>
+        <v>103021</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5778,10 +5778,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>680800</v>
+        <v>680871</v>
       </c>
       <c r="R51" t="n">
-        <v>7087109</v>
+        <v>7087130</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5828,12 +5828,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -5844,10 +5844,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126839954</v>
+        <v>126836213</v>
       </c>
       <c r="B52" t="n">
-        <v>57821</v>
+        <v>75135</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5855,21 +5855,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103021</v>
+        <v>6440</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5879,10 +5879,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>680871</v>
+        <v>680800</v>
       </c>
       <c r="R52" t="n">
-        <v>7087130</v>
+        <v>7087109</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5929,12 +5929,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -5945,10 +5945,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126838799</v>
+        <v>126836276</v>
       </c>
       <c r="B53" t="n">
-        <v>98469</v>
+        <v>97314</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5956,34 +5956,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Röjdtjärnviden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>680795</v>
+        <v>680857</v>
       </c>
       <c r="R53" t="n">
-        <v>7087239</v>
+        <v>7087050</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6030,22 +6030,26 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY53" t="inlineStr"/>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126836276</v>
+        <v>126838799</v>
       </c>
       <c r="B54" t="n">
-        <v>97325</v>
+        <v>98457</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6053,34 +6057,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221945</v>
+        <v>221952</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Röjdtjärnviden, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>680857</v>
+        <v>680795</v>
       </c>
       <c r="R54" t="n">
-        <v>7087050</v>
+        <v>7087239</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6127,19 +6131,15 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY54" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 64501-2023 artfynd.xlsx
+++ b/artfynd/A 64501-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY54"/>
+  <dimension ref="A1:AY57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6141,6 +6141,312 @@
         </is>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>133850787</v>
+      </c>
+      <c r="B55" t="n">
+        <v>91920</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Skogen, Ång</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>680811</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7087113</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-43</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Lukas Holmström</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Lukas Holmström</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>133850740</v>
+      </c>
+      <c r="B56" t="n">
+        <v>83316</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Skogen, Ång</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>680816</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7087100</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-83</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Lukas Holmström</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Lukas Holmström</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>133850738</v>
+      </c>
+      <c r="B57" t="n">
+        <v>83316</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Skogen, Ång</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>680809</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7087096</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-85</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Lukas Holmström</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Lukas Holmström</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 64501-2023 artfynd.xlsx
+++ b/artfynd/A 64501-2023 artfynd.xlsx
@@ -6146,7 +6146,7 @@
         <v>133850787</v>
       </c>
       <c r="B55" t="n">
-        <v>91920</v>
+        <v>91926</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6248,7 +6248,7 @@
         <v>133850740</v>
       </c>
       <c r="B56" t="n">
-        <v>83316</v>
+        <v>83318</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6350,7 +6350,7 @@
         <v>133850738</v>
       </c>
       <c r="B57" t="n">
-        <v>83316</v>
+        <v>83318</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 64501-2023 artfynd.xlsx
+++ b/artfynd/A 64501-2023 artfynd.xlsx
@@ -6146,7 +6146,7 @@
         <v>133850787</v>
       </c>
       <c r="B55" t="n">
-        <v>91926</v>
+        <v>91928</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6248,7 +6248,7 @@
         <v>133850740</v>
       </c>
       <c r="B56" t="n">
-        <v>83318</v>
+        <v>83319</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6350,7 +6350,7 @@
         <v>133850738</v>
       </c>
       <c r="B57" t="n">
-        <v>83318</v>
+        <v>83319</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 64501-2023 artfynd.xlsx
+++ b/artfynd/A 64501-2023 artfynd.xlsx
@@ -6146,7 +6146,7 @@
         <v>133850787</v>
       </c>
       <c r="B55" t="n">
-        <v>91928</v>
+        <v>91947</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6248,7 +6248,7 @@
         <v>133850740</v>
       </c>
       <c r="B56" t="n">
-        <v>83319</v>
+        <v>83333</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6350,7 +6350,7 @@
         <v>133850738</v>
       </c>
       <c r="B57" t="n">
-        <v>83319</v>
+        <v>83333</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 64501-2023 artfynd.xlsx
+++ b/artfynd/A 64501-2023 artfynd.xlsx
@@ -6146,7 +6146,7 @@
         <v>133850787</v>
       </c>
       <c r="B55" t="n">
-        <v>91947</v>
+        <v>91957</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6248,7 +6248,7 @@
         <v>133850740</v>
       </c>
       <c r="B56" t="n">
-        <v>83333</v>
+        <v>83343</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6350,7 +6350,7 @@
         <v>133850738</v>
       </c>
       <c r="B57" t="n">
-        <v>83333</v>
+        <v>83343</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 64501-2023 artfynd.xlsx
+++ b/artfynd/A 64501-2023 artfynd.xlsx
@@ -6146,7 +6146,7 @@
         <v>133850787</v>
       </c>
       <c r="B55" t="n">
-        <v>91957</v>
+        <v>91959</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6248,7 +6248,7 @@
         <v>133850740</v>
       </c>
       <c r="B56" t="n">
-        <v>83343</v>
+        <v>83344</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6350,7 +6350,7 @@
         <v>133850738</v>
       </c>
       <c r="B57" t="n">
-        <v>83343</v>
+        <v>83344</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 64501-2023 artfynd.xlsx
+++ b/artfynd/A 64501-2023 artfynd.xlsx
@@ -6146,7 +6146,7 @@
         <v>133850787</v>
       </c>
       <c r="B55" t="n">
-        <v>91960</v>
+        <v>91967</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6248,7 +6248,7 @@
         <v>133850740</v>
       </c>
       <c r="B56" t="n">
-        <v>83344</v>
+        <v>83351</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6350,7 +6350,7 @@
         <v>133850738</v>
       </c>
       <c r="B57" t="n">
-        <v>83344</v>
+        <v>83351</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>

--- a/artfynd/A 64501-2023 artfynd.xlsx
+++ b/artfynd/A 64501-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY57"/>
+  <dimension ref="A1:AY98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126836238</v>
+        <v>126839925</v>
       </c>
       <c r="B2" t="n">
-        <v>57821</v>
+        <v>83292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>680851</v>
+        <v>680859</v>
       </c>
       <c r="R2" t="n">
-        <v>7087009</v>
+        <v>7087090</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,12 +760,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126836222</v>
+        <v>126839980</v>
       </c>
       <c r="B3" t="n">
-        <v>91295</v>
+        <v>83292</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>680864</v>
+        <v>680796</v>
       </c>
       <c r="R3" t="n">
-        <v>7087088</v>
+        <v>7087081</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,12 +861,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126839924</v>
+        <v>126836540</v>
       </c>
       <c r="B4" t="n">
-        <v>75142</v>
+        <v>78993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>680859</v>
+        <v>680908</v>
       </c>
       <c r="R4" t="n">
-        <v>7087090</v>
+        <v>7087127</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -962,12 +962,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -978,10 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126839930</v>
+        <v>126840775</v>
       </c>
       <c r="B5" t="n">
-        <v>75142</v>
+        <v>78993</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -989,34 +989,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Lämkullen, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>680800</v>
+        <v>680905</v>
       </c>
       <c r="R5" t="n">
-        <v>7087070</v>
+        <v>7087125</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1046,29 +1049,40 @@
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Malin Löfgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1079,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126836455</v>
+        <v>126836226</v>
       </c>
       <c r="B6" t="n">
-        <v>79018</v>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,21 +1104,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1114,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>680796</v>
+        <v>680802</v>
       </c>
       <c r="R6" t="n">
-        <v>7087097</v>
+        <v>7086993</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1180,10 +1194,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126836264</v>
+        <v>126837045</v>
       </c>
       <c r="B7" t="n">
-        <v>57661</v>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,39 +1205,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>680811</v>
+        <v>680812</v>
       </c>
       <c r="R7" t="n">
-        <v>7087049</v>
+        <v>7086987</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1258,11 +1267,6 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>äldre ringhack (gran)</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1275,12 +1279,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1291,10 +1295,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126836229</v>
+        <v>133850787</v>
       </c>
       <c r="B8" t="n">
-        <v>57661</v>
+        <v>91974</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1302,38 +1306,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>680850</v>
+        <v>680811</v>
       </c>
       <c r="R8" t="n">
-        <v>7087177</v>
+        <v>7087113</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1360,12 +1360,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-43</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1380,58 +1385,54 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lukas Holmström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Lukas Holmström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126836243</v>
+        <v>126837053</v>
       </c>
       <c r="B9" t="n">
-        <v>98469</v>
+        <v>91930</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221952</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>680867</v>
+        <v>680770</v>
       </c>
       <c r="R9" t="n">
         <v>7087092</v>
@@ -1481,12 +1482,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1497,10 +1498,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126836248</v>
+        <v>126836222</v>
       </c>
       <c r="B10" t="n">
-        <v>80025</v>
+        <v>91872</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1508,21 +1509,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6456</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1532,10 +1533,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>680890</v>
+        <v>680864</v>
       </c>
       <c r="R10" t="n">
-        <v>7086899</v>
+        <v>7087088</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1598,50 +1599,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126839943</v>
+        <v>126836223</v>
       </c>
       <c r="B11" t="n">
-        <v>57661</v>
+        <v>91872</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>680794</v>
+        <v>680802</v>
       </c>
       <c r="R11" t="n">
-        <v>7087085</v>
+        <v>7087182</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1688,12 +1684,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1704,50 +1700,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126836499</v>
+        <v>126837036</v>
       </c>
       <c r="B12" t="n">
-        <v>57661</v>
+        <v>91872</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>680839</v>
+        <v>680865</v>
       </c>
       <c r="R12" t="n">
-        <v>7087048</v>
+        <v>7087035</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1794,12 +1785,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1810,50 +1801,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126836500</v>
+        <v>126837038</v>
       </c>
       <c r="B13" t="n">
-        <v>57661</v>
+        <v>91872</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>680809</v>
+        <v>680783</v>
       </c>
       <c r="R13" t="n">
-        <v>7087115</v>
+        <v>7087069</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1900,12 +1886,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1916,50 +1902,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126836258</v>
+        <v>133850750</v>
       </c>
       <c r="B14" t="n">
-        <v>57661</v>
+        <v>91937</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>680805</v>
+        <v>680777</v>
       </c>
       <c r="R14" t="n">
-        <v>7087122</v>
+        <v>7087100</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1986,17 +1967,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Äldre ringhack (gran) intill djupa körspår efter illegal avverkning genomförd av SCA</t>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-73</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2011,48 +1992,44 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lukas Holmström</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Lukas Holmström</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126839925</v>
+        <v>126836355</v>
       </c>
       <c r="B15" t="n">
-        <v>75127</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>306</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2062,10 +2039,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>680859</v>
+        <v>680779</v>
       </c>
       <c r="R15" t="n">
-        <v>7087090</v>
+        <v>7087023</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2112,12 +2089,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2128,50 +2105,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126836260</v>
+        <v>126836356</v>
       </c>
       <c r="B16" t="n">
-        <v>57661</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>680809</v>
+        <v>680782</v>
       </c>
       <c r="R16" t="n">
-        <v>7087061</v>
+        <v>7087012</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2204,11 +2176,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran) intill djupa körspår efter illegal avverkning genomförd av SCA</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2239,14 +2206,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126836451</v>
+        <v>126836357</v>
       </c>
       <c r="B17" t="n">
-        <v>79018</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2274,10 +2241,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>680864</v>
+        <v>680784</v>
       </c>
       <c r="R17" t="n">
-        <v>7087091</v>
+        <v>7087010</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2340,14 +2307,14 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126836465</v>
+        <v>126836358</v>
       </c>
       <c r="B18" t="n">
-        <v>79018</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2375,10 +2342,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>680782</v>
+        <v>680811</v>
       </c>
       <c r="R18" t="n">
-        <v>7087268</v>
+        <v>7086966</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2441,32 +2408,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126840006</v>
+        <v>126836359</v>
       </c>
       <c r="B19" t="n">
-        <v>8439</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106554</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2476,10 +2443,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>680902</v>
+        <v>680826</v>
       </c>
       <c r="R19" t="n">
-        <v>7087115</v>
+        <v>7086953</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2526,12 +2493,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2542,14 +2509,14 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126836452</v>
+        <v>126836360</v>
       </c>
       <c r="B20" t="n">
-        <v>79018</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2577,10 +2544,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>680856</v>
+        <v>680954</v>
       </c>
       <c r="R20" t="n">
-        <v>7087078</v>
+        <v>7086865</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2643,32 +2610,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126836282</v>
+        <v>126836448</v>
       </c>
       <c r="B21" t="n">
-        <v>80149</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2678,10 +2645,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>680867</v>
+        <v>680910</v>
       </c>
       <c r="R21" t="n">
-        <v>7087092</v>
+        <v>7087135</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2744,14 +2711,14 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126836454</v>
+        <v>126836450</v>
       </c>
       <c r="B22" t="n">
-        <v>79018</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -2779,10 +2746,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>680813</v>
+        <v>680892</v>
       </c>
       <c r="R22" t="n">
-        <v>7087014</v>
+        <v>7087111</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2845,45 +2812,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126838808</v>
+        <v>126836451</v>
       </c>
       <c r="B23" t="n">
-        <v>58031</v>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Röjdtjärnviden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>680797</v>
+        <v>680864</v>
       </c>
       <c r="R23" t="n">
-        <v>7087093</v>
+        <v>7087091</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2930,12 +2897,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -2946,32 +2913,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126839980</v>
+        <v>126836452</v>
       </c>
       <c r="B24" t="n">
-        <v>75127</v>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>306</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2981,10 +2948,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>680796</v>
+        <v>680856</v>
       </c>
       <c r="R24" t="n">
-        <v>7087081</v>
+        <v>7087078</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3031,12 +2998,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3047,48 +3014,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126840775</v>
+        <v>126836453</v>
       </c>
       <c r="B25" t="n">
-        <v>78685</v>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Lämkullen, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>680905</v>
+        <v>680855</v>
       </c>
       <c r="R25" t="n">
-        <v>7087125</v>
+        <v>7087023</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3118,40 +3082,29 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>11:49</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>11:49</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3162,32 +3115,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126836283</v>
+        <v>126836454</v>
       </c>
       <c r="B26" t="n">
-        <v>80149</v>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3197,10 +3150,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>680788</v>
+        <v>680813</v>
       </c>
       <c r="R26" t="n">
-        <v>7087194</v>
+        <v>7087014</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3263,14 +3216,14 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126836456</v>
+        <v>126836455</v>
       </c>
       <c r="B27" t="n">
-        <v>79018</v>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -3298,10 +3251,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>680813</v>
+        <v>680796</v>
       </c>
       <c r="R27" t="n">
-        <v>7087134</v>
+        <v>7087097</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3364,32 +3317,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126836223</v>
+        <v>126836456</v>
       </c>
       <c r="B28" t="n">
-        <v>91295</v>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3399,10 +3352,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>680802</v>
+        <v>680813</v>
       </c>
       <c r="R28" t="n">
-        <v>7087182</v>
+        <v>7087134</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3465,27 +3418,27 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126826864</v>
+        <v>126836457</v>
       </c>
       <c r="B29" t="n">
-        <v>80156</v>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3496,14 +3449,14 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Slagörkullen, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>680792</v>
+        <v>680830</v>
       </c>
       <c r="R29" t="n">
-        <v>7087098</v>
+        <v>7087203</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3533,19 +3486,9 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>11:15</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>11:15</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3560,12 +3503,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Malin Löfgren</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3576,14 +3519,14 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126836448</v>
+        <v>126836458</v>
       </c>
       <c r="B30" t="n">
-        <v>79018</v>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -3611,10 +3554,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>680910</v>
+        <v>680784</v>
       </c>
       <c r="R30" t="n">
-        <v>7087135</v>
+        <v>7087189</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3677,32 +3620,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126839926</v>
+        <v>126836460</v>
       </c>
       <c r="B31" t="n">
-        <v>75142</v>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3712,10 +3655,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>680847</v>
+        <v>680779</v>
       </c>
       <c r="R31" t="n">
-        <v>7087085</v>
+        <v>7087200</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3762,12 +3705,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3778,32 +3721,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126836239</v>
+        <v>126836461</v>
       </c>
       <c r="B32" t="n">
-        <v>80150</v>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3813,10 +3756,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>680791</v>
+        <v>680774</v>
       </c>
       <c r="R32" t="n">
-        <v>7087100</v>
+        <v>7087204</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3879,14 +3822,14 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126836457</v>
+        <v>126836462</v>
       </c>
       <c r="B33" t="n">
-        <v>79018</v>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -3914,10 +3857,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>680830</v>
+        <v>680777</v>
       </c>
       <c r="R33" t="n">
-        <v>7087203</v>
+        <v>7087215</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3980,32 +3923,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126836277</v>
+        <v>126836463</v>
       </c>
       <c r="B34" t="n">
-        <v>97325</v>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4015,10 +3958,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>680850</v>
+        <v>680773</v>
       </c>
       <c r="R34" t="n">
-        <v>7087177</v>
+        <v>7087233</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4081,45 +4024,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126838786</v>
+        <v>126836464</v>
       </c>
       <c r="B35" t="n">
-        <v>57661</v>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Röjdtjärnviden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>680812</v>
+        <v>680772</v>
       </c>
       <c r="R35" t="n">
-        <v>7087063</v>
+        <v>7087252</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4154,11 +4097,6 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4171,44 +4109,48 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr"/>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126836281</v>
+        <v>126836465</v>
       </c>
       <c r="B36" t="n">
-        <v>80149</v>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4218,10 +4160,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>680886</v>
+        <v>680782</v>
       </c>
       <c r="R36" t="n">
-        <v>7087103</v>
+        <v>7087268</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4284,32 +4226,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126839965</v>
+        <v>126836466</v>
       </c>
       <c r="B37" t="n">
-        <v>78777</v>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4319,10 +4261,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>680908</v>
+        <v>680756</v>
       </c>
       <c r="R37" t="n">
-        <v>7087111</v>
+        <v>7087273</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4369,12 +4311,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4385,32 +4327,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126836247</v>
+        <v>126836467</v>
       </c>
       <c r="B38" t="n">
-        <v>80025</v>
+        <v>79327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4420,10 +4362,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>680772</v>
+        <v>680758</v>
       </c>
       <c r="R38" t="n">
-        <v>7087294</v>
+        <v>7087267</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4456,11 +4398,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>På asplåga</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4491,14 +4428,14 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126836358</v>
+        <v>126836468</v>
       </c>
       <c r="B39" t="n">
-        <v>79018</v>
+        <v>79327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -4526,10 +4463,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>680811</v>
+        <v>680752</v>
       </c>
       <c r="R39" t="n">
-        <v>7086966</v>
+        <v>7087262</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4592,50 +4529,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126836263</v>
+        <v>126837082</v>
       </c>
       <c r="B40" t="n">
-        <v>57661</v>
+        <v>79327</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Rödtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>680847</v>
+        <v>680771</v>
       </c>
       <c r="R40" t="n">
-        <v>7087070</v>
+        <v>7087091</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4670,11 +4602,6 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>äldre ringhack (gran)</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -4687,12 +4614,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4703,14 +4630,14 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126836359</v>
+        <v>126838819</v>
       </c>
       <c r="B41" t="n">
-        <v>79018</v>
+        <v>79327</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -4734,14 +4661,14 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Röjdtjärnviden, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>680826</v>
+        <v>680868</v>
       </c>
       <c r="R41" t="n">
-        <v>7086953</v>
+        <v>7087031</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4788,12 +4715,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -4804,14 +4731,14 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126836450</v>
+        <v>126838821</v>
       </c>
       <c r="B42" t="n">
-        <v>79018</v>
+        <v>79327</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -4835,14 +4762,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Röjdtjärnviden, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>680892</v>
+        <v>680775</v>
       </c>
       <c r="R42" t="n">
-        <v>7087111</v>
+        <v>7087121</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4889,12 +4816,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -4905,45 +4832,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126839966</v>
+        <v>126838822</v>
       </c>
       <c r="B43" t="n">
-        <v>79636</v>
+        <v>79327</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Röjdtjärnviden, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>680908</v>
+        <v>680783</v>
       </c>
       <c r="R43" t="n">
-        <v>7087111</v>
+        <v>7087170</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4990,12 +4917,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Peder Winding</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5006,50 +4933,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126836266</v>
+        <v>126838823</v>
       </c>
       <c r="B44" t="n">
-        <v>57661</v>
+        <v>79327</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Röjdtjärnviden, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>680870</v>
+        <v>680767</v>
       </c>
       <c r="R44" t="n">
-        <v>7086922</v>
+        <v>7087204</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5084,11 +5006,6 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Färska ringhack på nyligen tillskapad högstubbe i samband med av SCA genomförd illegal avverkning</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5101,12 +5018,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5117,50 +5034,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126836265</v>
+        <v>126838824</v>
       </c>
       <c r="B45" t="n">
-        <v>57661</v>
+        <v>79327</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Röjdtjärnviden, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>680876</v>
+        <v>680778</v>
       </c>
       <c r="R45" t="n">
-        <v>7086899</v>
+        <v>7087226</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5195,11 +5107,6 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>färska ringhack (gran)</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5212,12 +5119,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5228,45 +5135,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126836540</v>
+        <v>126838825</v>
       </c>
       <c r="B46" t="n">
-        <v>78685</v>
+        <v>79327</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Röjdtjärnviden, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>680908</v>
+        <v>680759</v>
       </c>
       <c r="R46" t="n">
-        <v>7087127</v>
+        <v>7087282</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5313,12 +5220,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5329,14 +5236,14 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126836453</v>
+        <v>126839989</v>
       </c>
       <c r="B47" t="n">
-        <v>79018</v>
+        <v>79327</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
@@ -5364,10 +5271,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>680855</v>
+        <v>680774</v>
       </c>
       <c r="R47" t="n">
-        <v>7087023</v>
+        <v>7087124</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5414,12 +5321,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5430,32 +5337,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126836212</v>
+        <v>126839992</v>
       </c>
       <c r="B48" t="n">
-        <v>75142</v>
+        <v>79327</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5465,10 +5372,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>680844</v>
+        <v>680767</v>
       </c>
       <c r="R48" t="n">
-        <v>7087067</v>
+        <v>7087114</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5515,12 +5422,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5531,50 +5438,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126836267</v>
+        <v>133851012</v>
       </c>
       <c r="B49" t="n">
-        <v>57661</v>
+        <v>83341</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6439</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Röjdtjärnliden, Ång</t>
+          <t>Skogen, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>680851</v>
+        <v>680799</v>
       </c>
       <c r="R49" t="n">
-        <v>7087171</v>
+        <v>7087040</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5601,17 +5503,17 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>färska ringhack (gran)</t>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-60</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5626,26 +5528,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Lukas Holmström</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY49" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Lukas Holmström</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126837045</v>
+        <v>126836212</v>
       </c>
       <c r="B50" t="n">
-        <v>91330</v>
+        <v>83307</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5653,34 +5551,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Rödtjärnliden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>680812</v>
+        <v>680844</v>
       </c>
       <c r="R50" t="n">
-        <v>7086987</v>
+        <v>7087067</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5727,12 +5625,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Anders Heggestad, Malin Löfgren, Roger Adolfsson, Peder Winding</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -5746,7 +5644,7 @@
         <v>126836213</v>
       </c>
       <c r="B51" t="n">
-        <v>75142</v>
+        <v>83307</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5844,10 +5742,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126839954</v>
+        <v>126839924</v>
       </c>
       <c r="B52" t="n">
-        <v>57821</v>
+        <v>83307</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5855,21 +5753,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103021</v>
+        <v>6440</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5879,10 +5777,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>680871</v>
+        <v>680859</v>
       </c>
       <c r="R52" t="n">
-        <v>7087130</v>
+        <v>7087090</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5945,45 +5843,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126838799</v>
+        <v>126839926</v>
       </c>
       <c r="B53" t="n">
-        <v>98469</v>
+        <v>83307</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221952</v>
+        <v>6440</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Röjdtjärnviden, Ång</t>
+          <t>Röjdtjärnliden, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>680795</v>
+        <v>680847</v>
       </c>
       <c r="R53" t="n">
-        <v>7087239</v>
+        <v>7087085</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6030,44 +5928,48 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY53" t="inlineStr"/>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126836276</v>
+        <v>126839930</v>
       </c>
       <c r="B54" t="n">
-        <v>97325</v>
+        <v>83307</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221945</v>
+        <v>6440</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6077,10 +5979,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>680857</v>
+        <v>680800</v>
       </c>
       <c r="R54" t="n">
-        <v>7087050</v>
+        <v>7087070</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6127,12 +6029,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Peder Winding</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6143,10 +6045,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133850787</v>
+        <v>133850738</v>
       </c>
       <c r="B55" t="n">
-        <v>91967</v>
+        <v>83358</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6154,21 +6056,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6178,10 +6080,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>680811</v>
+        <v>680809</v>
       </c>
       <c r="R55" t="n">
-        <v>7087113</v>
+        <v>7087096</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6218,7 +6120,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-43</t>
+          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-85</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6248,7 +6150,7 @@
         <v>133850740</v>
       </c>
       <c r="B56" t="n">
-        <v>83351</v>
+        <v>83358</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6347,10 +6249,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>133850738</v>
+        <v>126838804</v>
       </c>
       <c r="B57" t="n">
-        <v>83351</v>
+        <v>79084</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6358,34 +6260,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6440</v>
+        <v>6446</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Skogen, Ång</t>
+          <t>Röjdtjärnviden, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>680809</v>
+        <v>680765</v>
       </c>
       <c r="R57" t="n">
-        <v>7087096</v>
+        <v>7087124</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6412,17 +6314,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Datum osäkert, men mellan 2024-05-05 och 2025-10-85</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6437,15 +6334,4282 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Lukas Holmström</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Lukas Holmström</t>
-        </is>
-      </c>
-      <c r="AY57" t="inlineStr"/>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>126839971</v>
+      </c>
+      <c r="B58" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Röjdtjärnliden, Ång</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>680772</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7087124</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>126839937</v>
+      </c>
+      <c r="B59" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Röjdtjärnliden, Ång</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>680761</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7087124</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>126839966</v>
+      </c>
+      <c r="B60" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Röjdtjärnliden, Ång</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>680908</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7087111</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>126836247</v>
+      </c>
+      <c r="B61" t="n">
+        <v>80336</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Röjdtjärnliden, Ång</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>680772</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7087294</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>På asplåga</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>126836248</v>
+      </c>
+      <c r="B62" t="n">
+        <v>80336</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Röjdtjärnliden, Ång</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>680890</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7086899</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>126836281</v>
+      </c>
+      <c r="B63" t="n">
+        <v>80460</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Röjdtjärnliden, Ång</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>680886</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7087103</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>126836282</v>
+      </c>
+      <c r="B64" t="n">
+        <v>80460</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Röjdtjärnliden, Ång</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>680867</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7087092</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>126836283</v>
+      </c>
+      <c r="B65" t="n">
+        <v>80460</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Röjdtjärnliden, Ång</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>680788</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7087194</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>126836239</v>
+      </c>
+      <c r="B66" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Röjdtjärnliden, Ång</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>680791</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7087100</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>126826864</v>
+      </c>
+      <c r="B67" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Slagörkullen, Ång</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>680792</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7087098</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Malin Löfgren</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Malin Löfgren</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>126836229</v>
+      </c>
+      <c r="B68" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Röjdtjärnliden, Ång</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>680850</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7087177</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>126836258</v>
+      </c>
+      <c r="B69" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Röjdtjärnliden, Ång</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>680805</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7087122</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran) intill djupa körspår efter illegal avverkning genomförd av SCA</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>126836260</v>
+      </c>
+      <c r="B70" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Röjdtjärnliden, Ång</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>680809</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7087061</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran) intill djupa körspår efter illegal avverkning genomförd av SCA</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>126836261</v>
+      </c>
+      <c r="B71" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Röjdtjärnliden, Ång</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>680939</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7086837</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>äldre ringhack (gran)</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>126836262</v>
+      </c>
+      <c r="B72" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Röjdtjärnliden, Ång</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>680948</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7086853</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>äldre ringhack (gran)</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>126836263</v>
+      </c>
+      <c r="B73" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Röjdtjärnliden, Ång</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>680847</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7087070</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>äldre ringhack (gran)</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>126836264</v>
+      </c>
+      <c r="B74" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Röjdtjärnliden, Ång</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>680811</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7087049</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>äldre ringhack (gran)</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>126836265</v>
+      </c>
+      <c r="B75" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Röjdtjärnliden, Ång</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>680876</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7086899</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>färska ringhack (gran)</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>126836266</v>
+      </c>
+      <c r="B76" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Röjdtjärnliden, Ång</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>680870</v>
+      </c>
+      <c r="R76" t="n">
+        <v>7086922</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Färska ringhack på nyligen tillskapad högstubbe i samband med av SCA genomförd illegal avverkning</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>126836267</v>
+      </c>
+      <c r="B77" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Röjdtjärnliden, Ång</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>680851</v>
+      </c>
+      <c r="R77" t="n">
+        <v>7087171</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>färska ringhack (gran)</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>126836499</v>
+      </c>
+      <c r="B78" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Röjdtjärnliden, Ång</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>680839</v>
+      </c>
+      <c r="R78" t="n">
+        <v>7087048</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>126836500</v>
+      </c>
+      <c r="B79" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Röjdtjärnliden, Ång</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>680809</v>
+      </c>
+      <c r="R79" t="n">
+        <v>7087115</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>126838786</v>
+      </c>
+      <c r="B80" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Röjdtjärnviden, Ång</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>680812</v>
+      </c>
+      <c r="R80" t="n">
+        <v>7087063</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>126839943</v>
+      </c>
+      <c r="B81" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Röjdtjärnliden, Ång</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>680794</v>
+      </c>
+      <c r="R81" t="n">
+        <v>7087085</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>126836230</v>
+      </c>
+      <c r="B82" t="n">
+        <v>57774</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>102976</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Tornseglare</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Apus apus</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Röjdtjärnliden, Ång</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>680774</v>
+      </c>
+      <c r="R82" t="n">
+        <v>7087234</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>126838808</v>
+      </c>
+      <c r="B83" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Röjdtjärnviden, Ång</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>680797</v>
+      </c>
+      <c r="R83" t="n">
+        <v>7087093</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>126836238</v>
+      </c>
+      <c r="B84" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Röjdtjärnliden, Ång</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>680851</v>
+      </c>
+      <c r="R84" t="n">
+        <v>7087009</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>126838797</v>
+      </c>
+      <c r="B85" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Röjdtjärnviden, Ång</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>680872</v>
+      </c>
+      <c r="R85" t="n">
+        <v>7087043</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>126838798</v>
+      </c>
+      <c r="B86" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Röjdtjärnviden, Ång</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>680781</v>
+      </c>
+      <c r="R86" t="n">
+        <v>7087170</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>126839954</v>
+      </c>
+      <c r="B87" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Röjdtjärnliden, Ång</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>680871</v>
+      </c>
+      <c r="R87" t="n">
+        <v>7087130</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>126840006</v>
+      </c>
+      <c r="B88" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Röjdtjärnliden, Ång</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>680902</v>
+      </c>
+      <c r="R88" t="n">
+        <v>7087115</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>126836333</v>
+      </c>
+      <c r="B89" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Röjdtjärnliden, Ång</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>680975</v>
+      </c>
+      <c r="R89" t="n">
+        <v>7087105</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>126836268</v>
+      </c>
+      <c r="B90" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Röjdtjärnliden, Ång</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>680935</v>
+      </c>
+      <c r="R90" t="n">
+        <v>7086838</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>126836276</v>
+      </c>
+      <c r="B91" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Röjdtjärnliden, Ång</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>680857</v>
+      </c>
+      <c r="R91" t="n">
+        <v>7087050</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>126836277</v>
+      </c>
+      <c r="B92" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Röjdtjärnliden, Ång</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>680850</v>
+      </c>
+      <c r="R92" t="n">
+        <v>7087177</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>126836243</v>
+      </c>
+      <c r="B93" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Röjdtjärnliden, Ång</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>680867</v>
+      </c>
+      <c r="R93" t="n">
+        <v>7087092</v>
+      </c>
+      <c r="S93" t="n">
+        <v>10</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>126838799</v>
+      </c>
+      <c r="B94" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Röjdtjärnviden, Ång</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>680795</v>
+      </c>
+      <c r="R94" t="n">
+        <v>7087239</v>
+      </c>
+      <c r="S94" t="n">
+        <v>10</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>126839965</v>
+      </c>
+      <c r="B95" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Röjdtjärnliden, Ång</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>680908</v>
+      </c>
+      <c r="R95" t="n">
+        <v>7087111</v>
+      </c>
+      <c r="S95" t="n">
+        <v>10</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>126839970</v>
+      </c>
+      <c r="B96" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Röjdtjärnliden, Ång</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>680772</v>
+      </c>
+      <c r="R96" t="n">
+        <v>7087124</v>
+      </c>
+      <c r="S96" t="n">
+        <v>10</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>126839990</v>
+      </c>
+      <c r="B97" t="n">
+        <v>79350</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Röjdtjärnliden, Ång</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>680774</v>
+      </c>
+      <c r="R97" t="n">
+        <v>7087124</v>
+      </c>
+      <c r="S97" t="n">
+        <v>10</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>126839991</v>
+      </c>
+      <c r="B98" t="n">
+        <v>79350</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Röjdtjärnliden, Ång</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>680767</v>
+      </c>
+      <c r="R98" t="n">
+        <v>7087114</v>
+      </c>
+      <c r="S98" t="n">
+        <v>10</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Peder Winding</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 64501-2023 artfynd.xlsx
+++ b/artfynd/A 64501-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY98"/>
+  <dimension ref="A1:AZ98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126839925</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126839980</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
       <c r="AY4" t="inlineStr">
         <is>
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836540</t>
         </is>
       </c>
     </row>
@@ -1090,6 +1110,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126840775</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1191,6 +1216,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836226</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1292,6 +1322,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126837045</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1394,6 +1429,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133850787</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1495,6 +1535,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126837053</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1596,6 +1641,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836222</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1697,6 +1747,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836223</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1798,6 +1853,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126837036</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1899,6 +1959,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126837038</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2001,6 +2066,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133850750</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2102,6 +2172,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836355</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2203,6 +2278,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836356</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2304,6 +2384,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836357</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2405,6 +2490,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836358</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2506,6 +2596,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836359</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2607,6 +2702,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836360</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2708,6 +2808,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836448</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2809,6 +2914,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836450</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2910,6 +3020,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836451</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3011,6 +3126,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836452</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3112,6 +3232,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836453</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3213,6 +3338,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836454</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3314,6 +3444,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836455</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3415,6 +3550,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836456</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3516,6 +3656,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836457</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3617,6 +3762,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836458</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3718,6 +3868,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836460</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3819,6 +3974,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836461</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3920,6 +4080,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836462</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4021,6 +4186,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836463</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4122,6 +4292,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836464</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4223,6 +4398,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836465</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4324,6 +4504,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836466</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4425,6 +4610,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836467</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4526,6 +4716,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836468</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4627,6 +4822,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126837082</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4728,6 +4928,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126838819</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4829,6 +5034,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126838821</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4930,6 +5140,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126838822</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5031,6 +5246,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126838823</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5132,6 +5352,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126838824</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5233,6 +5458,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126838825</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5334,6 +5564,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126839989</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5435,6 +5670,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126839992</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5537,6 +5777,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133851012</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5638,6 +5883,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836212</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5739,6 +5989,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836213</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5840,6 +6095,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126839924</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5941,6 +6201,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126839926</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6042,6 +6307,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126839930</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6144,6 +6414,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133850738</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6246,6 +6521,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133850740</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6347,6 +6627,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126838804</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6448,6 +6733,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126839971</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6549,6 +6839,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126839937</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6650,6 +6945,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126839966</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6756,6 +7056,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836247</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6857,6 +7162,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836248</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6958,6 +7268,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836281</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7059,6 +7374,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836282</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7160,6 +7480,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836283</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7261,6 +7586,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836239</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7372,6 +7702,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126826864</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7477,6 +7812,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836229</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7588,6 +7928,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836258</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7699,6 +8044,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836260</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7810,6 +8160,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836261</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7921,6 +8276,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836262</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8032,6 +8392,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836263</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8143,6 +8508,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836264</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8254,6 +8624,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836265</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8365,6 +8740,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836266</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8476,6 +8856,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836267</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8582,6 +8967,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836499</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8688,6 +9078,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836500</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8790,6 +9185,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126838786</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8896,6 +9296,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126839943</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8997,6 +9402,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836230</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9098,6 +9508,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126838808</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9199,6 +9614,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836238</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9296,6 +9716,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126838797</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9393,6 +9818,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126838798</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9494,6 +9924,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126839954</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9595,6 +10030,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126840006</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9705,6 +10145,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836333</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9806,6 +10251,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836268</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9907,6 +10357,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836276</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10008,6 +10463,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836277</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10109,6 +10569,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126836243</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10206,6 +10671,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126838799</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10307,6 +10777,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126839965</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10408,6 +10883,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126839970</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10509,6 +10989,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126839990</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10610,8 +11095,112 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126839991</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>